--- a/assets/templates/template_b2s.xlsx
+++ b/assets/templates/template_b2s.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\php8\htdocs\tower\assets\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0514B334-835C-4D9E-B302-C8034290C89C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{417EFB64-508A-46FB-A2D7-E4B77C1624EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" tabRatio="859" firstSheet="2" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" tabRatio="859" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stacking Shelter Checklist" sheetId="10" state="hidden" r:id="rId1"/>
     <sheet name="QC Point and Checklist" sheetId="6" state="hidden" r:id="rId2"/>
-    <sheet name="MASTER " sheetId="59" r:id="rId3"/>
-    <sheet name="CHECKLIS MK B2S  " sheetId="61" r:id="rId4"/>
+    <sheet name="MASTER" sheetId="59" r:id="rId3"/>
+    <sheet name="CHECKLIS MK B2S" sheetId="61" r:id="rId4"/>
     <sheet name="EVIDEN" sheetId="70" r:id="rId5"/>
     <sheet name="EVIDEN 1" sheetId="71" r:id="rId6"/>
     <sheet name="EVIDEN 2" sheetId="77" r:id="rId7"/>
@@ -30,7 +30,7 @@
     <sheet name="PENGECORAN SITE" sheetId="30" r:id="rId15"/>
     <sheet name="MOS &amp; ERECTION" sheetId="31" r:id="rId16"/>
     <sheet name="UNDANGAN ATP" sheetId="67" r:id="rId17"/>
-    <sheet name="PELAKSANAAN ATP " sheetId="58" r:id="rId18"/>
+    <sheet name="PELAKSANAAN ATP" sheetId="58" r:id="rId18"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId19"/>
@@ -1073,16 +1073,16 @@
     <definedName name="Position">#REF!</definedName>
     <definedName name="possatpam">[13]Validation!$N$1:$N$3</definedName>
     <definedName name="powerhouse">[7]Validation!$I$1:$I$6</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'CHECKLIS MK B2S  '!$A$1:$H$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'CHECKLIS MK B2S'!$A$1:$H$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="15">'MOS &amp; ERECTION'!$A$1:$K$59</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="17">'PELAKSANAAN ATP '!$A$1:$K$218</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="17">'PELAKSANAAN ATP'!$A$1:$K$218</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="14">'PENGECORAN SITE'!$A$1:$K$73</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="11">SKOM!$A$1:$K$42</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Stacking Shelter Checklist'!$A$1:$V$63</definedName>
     <definedName name="_xlnm.Print_Area">#REF!</definedName>
     <definedName name="Print_Area_MI">#REF!</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="15">'MOS &amp; ERECTION'!$1:$6</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="17">'PELAKSANAAN ATP '!$1:$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="17">'PELAKSANAAN ATP'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="14">'PENGECORAN SITE'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles">#REF!</definedName>
     <definedName name="Print_Titles_MI">#REF!</definedName>
@@ -1443,17 +1443,6 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <fileRecoveryPr autoRecover="0"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -1499,7 +1488,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="222">
   <si>
     <t>Minor</t>
   </si>
@@ -2121,9 +2110,6 @@
     <t xml:space="preserve">PENGUKURAN TEGANGAN </t>
   </si>
   <si>
-    <t xml:space="preserve">TSEL </t>
-  </si>
-  <si>
     <t xml:space="preserve"> PENGECORAN </t>
   </si>
   <si>
@@ -2166,58 +2152,19 @@
     <t>PENGUKURAN TEGANGAN ST</t>
   </si>
   <si>
-    <t>B2S</t>
-  </si>
-  <si>
     <t>EVIDEN</t>
   </si>
   <si>
     <t>DONE</t>
   </si>
   <si>
-    <t>Jabodetabeb</t>
-  </si>
-  <si>
     <t>PT. TRITECH CONSULT INDONESIA</t>
-  </si>
-  <si>
-    <t>Rizal Biruni</t>
-  </si>
-  <si>
-    <t>Agung Budi Hermawan</t>
-  </si>
-  <si>
-    <t>Ihsan Perbawa Ginanjar</t>
   </si>
   <si>
     <t>PEMBESIAN SITE</t>
   </si>
   <si>
-    <t>SST Triangle</t>
-  </si>
-  <si>
     <t>VERTICALITY</t>
-  </si>
-  <si>
-    <t>72M</t>
-  </si>
-  <si>
-    <t>Gempol Ragas</t>
-  </si>
-  <si>
-    <t>107.06629</t>
-  </si>
-  <si>
-    <t>-6.16459</t>
-  </si>
-  <si>
-    <t>Kp. Gabus Gedong, RT.006/RW.001, Desa Srijaya, Kec. Tambun Utara, Kab. Bekasi. Jawa Barat.</t>
-  </si>
-  <si>
-    <t>BKS395</t>
-  </si>
-  <si>
-    <t>24TS09B310</t>
   </si>
 </sst>
 </file>
@@ -4097,7 +4044,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="317">
+  <cellXfs count="316">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4584,22 +4531,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4609,60 +4547,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4713,7 +4597,25 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4724,6 +4626,51 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4770,6 +4717,57 @@
     <xf numFmtId="0" fontId="38" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="29" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="167" fontId="29" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="9" borderId="14" xfId="932" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="932" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="9" borderId="3" xfId="932" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="9" borderId="38" xfId="932" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="9" borderId="39" xfId="932" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="932" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="932" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -4806,57 +4804,6 @@
     <xf numFmtId="0" fontId="31" fillId="9" borderId="34" xfId="932" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="9" borderId="14" xfId="932" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="932" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="9" borderId="3" xfId="932" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="932" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="29" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="167" fontId="29" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="9" borderId="38" xfId="932" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="9" borderId="39" xfId="932" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4883,6 +4830,9 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4911,16 +4861,10 @@
     <xf numFmtId="0" fontId="47" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -42436,27 +42380,27 @@
       <c r="C1" s="196"/>
       <c r="D1" s="196"/>
       <c r="E1" s="197"/>
-      <c r="F1" s="231" t="s">
+      <c r="F1" s="210" t="s">
         <v>55</v>
       </c>
-      <c r="G1" s="232"/>
-      <c r="H1" s="232"/>
-      <c r="I1" s="232"/>
-      <c r="J1" s="232"/>
-      <c r="K1" s="232"/>
-      <c r="L1" s="232"/>
-      <c r="M1" s="232"/>
-      <c r="N1" s="232"/>
-      <c r="O1" s="232"/>
-      <c r="P1" s="232"/>
-      <c r="Q1" s="233"/>
-      <c r="R1" s="234" t="s">
+      <c r="G1" s="211"/>
+      <c r="H1" s="211"/>
+      <c r="I1" s="211"/>
+      <c r="J1" s="211"/>
+      <c r="K1" s="211"/>
+      <c r="L1" s="211"/>
+      <c r="M1" s="211"/>
+      <c r="N1" s="211"/>
+      <c r="O1" s="211"/>
+      <c r="P1" s="211"/>
+      <c r="Q1" s="212"/>
+      <c r="R1" s="213" t="s">
         <v>56</v>
       </c>
-      <c r="S1" s="235"/>
-      <c r="T1" s="235"/>
-      <c r="U1" s="235"/>
-      <c r="V1" s="236"/>
+      <c r="S1" s="214"/>
+      <c r="T1" s="214"/>
+      <c r="U1" s="214"/>
+      <c r="V1" s="215"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" s="198"/>
@@ -42480,11 +42424,11 @@
       <c r="O2" s="14"/>
       <c r="P2" s="22"/>
       <c r="Q2" s="22"/>
-      <c r="R2" s="237"/>
-      <c r="S2" s="238"/>
-      <c r="T2" s="238"/>
-      <c r="U2" s="238"/>
-      <c r="V2" s="239"/>
+      <c r="R2" s="216"/>
+      <c r="S2" s="217"/>
+      <c r="T2" s="217"/>
+      <c r="U2" s="217"/>
+      <c r="V2" s="218"/>
     </row>
     <row r="3" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="201"/>
@@ -42508,67 +42452,67 @@
       <c r="O3" s="14"/>
       <c r="P3" s="22"/>
       <c r="Q3" s="22"/>
-      <c r="R3" s="240"/>
-      <c r="S3" s="241"/>
-      <c r="T3" s="241"/>
-      <c r="U3" s="241"/>
-      <c r="V3" s="242"/>
+      <c r="R3" s="219"/>
+      <c r="S3" s="220"/>
+      <c r="T3" s="220"/>
+      <c r="U3" s="220"/>
+      <c r="V3" s="221"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" s="21"/>
       <c r="B4" s="21"/>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A5" s="246" t="s">
+      <c r="A5" s="225" t="s">
         <v>140</v>
       </c>
-      <c r="B5" s="246"/>
-      <c r="C5" s="246"/>
-      <c r="D5" s="246"/>
-      <c r="E5" s="246"/>
-      <c r="F5" s="246"/>
-      <c r="G5" s="246"/>
-      <c r="H5" s="246"/>
-      <c r="I5" s="246"/>
-      <c r="J5" s="246"/>
-      <c r="K5" s="246"/>
-      <c r="L5" s="246"/>
-      <c r="M5" s="246"/>
-      <c r="N5" s="246"/>
-      <c r="O5" s="246"/>
-      <c r="P5" s="246"/>
-      <c r="Q5" s="246"/>
-      <c r="R5" s="246"/>
-      <c r="S5" s="246"/>
-      <c r="T5" s="246"/>
-      <c r="U5" s="246"/>
-      <c r="V5" s="246"/>
+      <c r="B5" s="225"/>
+      <c r="C5" s="225"/>
+      <c r="D5" s="225"/>
+      <c r="E5" s="225"/>
+      <c r="F5" s="225"/>
+      <c r="G5" s="225"/>
+      <c r="H5" s="225"/>
+      <c r="I5" s="225"/>
+      <c r="J5" s="225"/>
+      <c r="K5" s="225"/>
+      <c r="L5" s="225"/>
+      <c r="M5" s="225"/>
+      <c r="N5" s="225"/>
+      <c r="O5" s="225"/>
+      <c r="P5" s="225"/>
+      <c r="Q5" s="225"/>
+      <c r="R5" s="225"/>
+      <c r="S5" s="225"/>
+      <c r="T5" s="225"/>
+      <c r="U5" s="225"/>
+      <c r="V5" s="225"/>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A6" s="243" t="s">
+      <c r="A6" s="222" t="s">
         <v>78</v>
       </c>
-      <c r="B6" s="244"/>
-      <c r="C6" s="244"/>
-      <c r="D6" s="244"/>
-      <c r="E6" s="244"/>
-      <c r="F6" s="244"/>
-      <c r="G6" s="244"/>
-      <c r="H6" s="244"/>
-      <c r="I6" s="244"/>
-      <c r="J6" s="244"/>
-      <c r="K6" s="244"/>
-      <c r="L6" s="244"/>
-      <c r="M6" s="244"/>
-      <c r="N6" s="244"/>
-      <c r="O6" s="244"/>
-      <c r="P6" s="244"/>
-      <c r="Q6" s="244"/>
-      <c r="R6" s="244"/>
-      <c r="S6" s="244"/>
-      <c r="T6" s="244"/>
-      <c r="U6" s="244"/>
-      <c r="V6" s="245"/>
+      <c r="B6" s="223"/>
+      <c r="C6" s="223"/>
+      <c r="D6" s="223"/>
+      <c r="E6" s="223"/>
+      <c r="F6" s="223"/>
+      <c r="G6" s="223"/>
+      <c r="H6" s="223"/>
+      <c r="I6" s="223"/>
+      <c r="J6" s="223"/>
+      <c r="K6" s="223"/>
+      <c r="L6" s="223"/>
+      <c r="M6" s="223"/>
+      <c r="N6" s="223"/>
+      <c r="O6" s="223"/>
+      <c r="P6" s="223"/>
+      <c r="Q6" s="223"/>
+      <c r="R6" s="223"/>
+      <c r="S6" s="223"/>
+      <c r="T6" s="223"/>
+      <c r="U6" s="223"/>
+      <c r="V6" s="224"/>
     </row>
     <row r="7" spans="1:25" ht="7.15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -42851,30 +42795,30 @@
       <c r="V17" s="57"/>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A18" s="243" t="s">
+      <c r="A18" s="222" t="s">
         <v>73</v>
       </c>
-      <c r="B18" s="244"/>
-      <c r="C18" s="244"/>
-      <c r="D18" s="244"/>
-      <c r="E18" s="244"/>
-      <c r="F18" s="244"/>
-      <c r="G18" s="244"/>
-      <c r="H18" s="244"/>
-      <c r="I18" s="244"/>
-      <c r="J18" s="244"/>
-      <c r="K18" s="244"/>
-      <c r="L18" s="244"/>
-      <c r="M18" s="244"/>
-      <c r="N18" s="244"/>
-      <c r="O18" s="244"/>
-      <c r="P18" s="244"/>
-      <c r="Q18" s="244"/>
-      <c r="R18" s="244"/>
-      <c r="S18" s="244"/>
-      <c r="T18" s="244"/>
-      <c r="U18" s="244"/>
-      <c r="V18" s="245"/>
+      <c r="B18" s="223"/>
+      <c r="C18" s="223"/>
+      <c r="D18" s="223"/>
+      <c r="E18" s="223"/>
+      <c r="F18" s="223"/>
+      <c r="G18" s="223"/>
+      <c r="H18" s="223"/>
+      <c r="I18" s="223"/>
+      <c r="J18" s="223"/>
+      <c r="K18" s="223"/>
+      <c r="L18" s="223"/>
+      <c r="M18" s="223"/>
+      <c r="N18" s="223"/>
+      <c r="O18" s="223"/>
+      <c r="P18" s="223"/>
+      <c r="Q18" s="223"/>
+      <c r="R18" s="223"/>
+      <c r="S18" s="223"/>
+      <c r="T18" s="223"/>
+      <c r="U18" s="223"/>
+      <c r="V18" s="224"/>
     </row>
     <row r="19" spans="1:22" ht="7.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="57"/>
@@ -42901,34 +42845,34 @@
       <c r="V19" s="57"/>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A20" s="207" t="s">
+      <c r="A20" s="229" t="s">
         <v>66</v>
       </c>
-      <c r="B20" s="209"/>
-      <c r="C20" s="207" t="s">
+      <c r="B20" s="230"/>
+      <c r="C20" s="229" t="s">
         <v>67</v>
       </c>
-      <c r="D20" s="208"/>
-      <c r="E20" s="208"/>
-      <c r="F20" s="208"/>
-      <c r="G20" s="208"/>
-      <c r="H20" s="208"/>
-      <c r="I20" s="208"/>
-      <c r="J20" s="208"/>
-      <c r="K20" s="208"/>
-      <c r="L20" s="209"/>
-      <c r="M20" s="247" t="s">
+      <c r="D20" s="232"/>
+      <c r="E20" s="232"/>
+      <c r="F20" s="232"/>
+      <c r="G20" s="232"/>
+      <c r="H20" s="232"/>
+      <c r="I20" s="232"/>
+      <c r="J20" s="232"/>
+      <c r="K20" s="232"/>
+      <c r="L20" s="230"/>
+      <c r="M20" s="231" t="s">
         <v>68</v>
       </c>
-      <c r="N20" s="247"/>
-      <c r="O20" s="247"/>
-      <c r="P20" s="207" t="s">
+      <c r="N20" s="231"/>
+      <c r="O20" s="231"/>
+      <c r="P20" s="229" t="s">
         <v>137</v>
       </c>
-      <c r="Q20" s="208"/>
-      <c r="R20" s="208"/>
-      <c r="S20" s="208"/>
-      <c r="T20" s="209"/>
+      <c r="Q20" s="232"/>
+      <c r="R20" s="232"/>
+      <c r="S20" s="232"/>
+      <c r="T20" s="230"/>
       <c r="U20" s="64" t="s">
         <v>69</v>
       </c>
@@ -42956,11 +42900,11 @@
       <c r="O21" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="P21" s="248"/>
-      <c r="Q21" s="249"/>
-      <c r="R21" s="249"/>
-      <c r="S21" s="249"/>
-      <c r="T21" s="250"/>
+      <c r="P21" s="233"/>
+      <c r="Q21" s="234"/>
+      <c r="R21" s="234"/>
+      <c r="S21" s="234"/>
+      <c r="T21" s="235"/>
       <c r="U21" s="32"/>
       <c r="V21" s="33"/>
     </row>
@@ -42984,11 +42928,11 @@
       <c r="M22" s="76"/>
       <c r="N22" s="76"/>
       <c r="O22" s="76"/>
-      <c r="P22" s="204"/>
-      <c r="Q22" s="205"/>
-      <c r="R22" s="205"/>
-      <c r="S22" s="205"/>
-      <c r="T22" s="206"/>
+      <c r="P22" s="226"/>
+      <c r="Q22" s="227"/>
+      <c r="R22" s="227"/>
+      <c r="S22" s="227"/>
+      <c r="T22" s="228"/>
       <c r="U22" s="59"/>
       <c r="V22" s="61"/>
     </row>
@@ -43012,11 +42956,11 @@
       <c r="M23" s="76"/>
       <c r="N23" s="76"/>
       <c r="O23" s="76"/>
-      <c r="P23" s="204"/>
-      <c r="Q23" s="205"/>
-      <c r="R23" s="205"/>
-      <c r="S23" s="205"/>
-      <c r="T23" s="206"/>
+      <c r="P23" s="226"/>
+      <c r="Q23" s="227"/>
+      <c r="R23" s="227"/>
+      <c r="S23" s="227"/>
+      <c r="T23" s="228"/>
       <c r="U23" s="59"/>
       <c r="V23" s="61"/>
     </row>
@@ -43040,11 +42984,11 @@
       <c r="M24" s="76"/>
       <c r="N24" s="76"/>
       <c r="O24" s="76"/>
-      <c r="P24" s="204"/>
-      <c r="Q24" s="205"/>
-      <c r="R24" s="205"/>
-      <c r="S24" s="205"/>
-      <c r="T24" s="206"/>
+      <c r="P24" s="226"/>
+      <c r="Q24" s="227"/>
+      <c r="R24" s="227"/>
+      <c r="S24" s="227"/>
+      <c r="T24" s="228"/>
       <c r="U24" s="59"/>
       <c r="V24" s="61"/>
     </row>
@@ -43066,13 +43010,13 @@
       <c r="M25" s="76"/>
       <c r="N25" s="76"/>
       <c r="O25" s="76"/>
-      <c r="P25" s="204" t="s">
+      <c r="P25" s="226" t="s">
         <v>122</v>
       </c>
-      <c r="Q25" s="205"/>
-      <c r="R25" s="205"/>
-      <c r="S25" s="205"/>
-      <c r="T25" s="206"/>
+      <c r="Q25" s="227"/>
+      <c r="R25" s="227"/>
+      <c r="S25" s="227"/>
+      <c r="T25" s="228"/>
       <c r="U25" s="59"/>
       <c r="V25" s="61"/>
     </row>
@@ -43094,13 +43038,13 @@
       <c r="M26" s="76"/>
       <c r="N26" s="76"/>
       <c r="O26" s="76"/>
-      <c r="P26" s="204" t="s">
+      <c r="P26" s="226" t="s">
         <v>122</v>
       </c>
-      <c r="Q26" s="205"/>
-      <c r="R26" s="205"/>
-      <c r="S26" s="205"/>
-      <c r="T26" s="206"/>
+      <c r="Q26" s="227"/>
+      <c r="R26" s="227"/>
+      <c r="S26" s="227"/>
+      <c r="T26" s="228"/>
       <c r="U26" s="59"/>
       <c r="V26" s="61"/>
     </row>
@@ -43122,13 +43066,13 @@
       <c r="M27" s="76"/>
       <c r="N27" s="76"/>
       <c r="O27" s="76"/>
-      <c r="P27" s="204" t="s">
+      <c r="P27" s="226" t="s">
         <v>122</v>
       </c>
-      <c r="Q27" s="205"/>
-      <c r="R27" s="205"/>
-      <c r="S27" s="205"/>
-      <c r="T27" s="206"/>
+      <c r="Q27" s="227"/>
+      <c r="R27" s="227"/>
+      <c r="S27" s="227"/>
+      <c r="T27" s="228"/>
       <c r="U27" s="59"/>
       <c r="V27" s="61"/>
     </row>
@@ -43152,11 +43096,11 @@
       <c r="M28" s="76"/>
       <c r="N28" s="76"/>
       <c r="O28" s="76"/>
-      <c r="P28" s="204"/>
-      <c r="Q28" s="205"/>
-      <c r="R28" s="205"/>
-      <c r="S28" s="205"/>
-      <c r="T28" s="206"/>
+      <c r="P28" s="226"/>
+      <c r="Q28" s="227"/>
+      <c r="R28" s="227"/>
+      <c r="S28" s="227"/>
+      <c r="T28" s="228"/>
       <c r="U28" s="59"/>
       <c r="V28" s="61"/>
     </row>
@@ -43178,13 +43122,13 @@
       <c r="M29" s="76"/>
       <c r="N29" s="76"/>
       <c r="O29" s="76"/>
-      <c r="P29" s="204" t="s">
+      <c r="P29" s="226" t="s">
         <v>123</v>
       </c>
-      <c r="Q29" s="205"/>
-      <c r="R29" s="205"/>
-      <c r="S29" s="205"/>
-      <c r="T29" s="206"/>
+      <c r="Q29" s="227"/>
+      <c r="R29" s="227"/>
+      <c r="S29" s="227"/>
+      <c r="T29" s="228"/>
       <c r="U29" s="59"/>
       <c r="V29" s="61"/>
     </row>
@@ -43206,13 +43150,13 @@
       <c r="M30" s="76"/>
       <c r="N30" s="76"/>
       <c r="O30" s="76"/>
-      <c r="P30" s="204" t="s">
+      <c r="P30" s="226" t="s">
         <v>44</v>
       </c>
-      <c r="Q30" s="205"/>
-      <c r="R30" s="205"/>
-      <c r="S30" s="205"/>
-      <c r="T30" s="206"/>
+      <c r="Q30" s="227"/>
+      <c r="R30" s="227"/>
+      <c r="S30" s="227"/>
+      <c r="T30" s="228"/>
       <c r="U30" s="59"/>
       <c r="V30" s="61"/>
     </row>
@@ -43236,11 +43180,11 @@
       <c r="M31" s="76"/>
       <c r="N31" s="76"/>
       <c r="O31" s="76"/>
-      <c r="P31" s="204"/>
-      <c r="Q31" s="205"/>
-      <c r="R31" s="205"/>
-      <c r="S31" s="205"/>
-      <c r="T31" s="206"/>
+      <c r="P31" s="226"/>
+      <c r="Q31" s="227"/>
+      <c r="R31" s="227"/>
+      <c r="S31" s="227"/>
+      <c r="T31" s="228"/>
       <c r="U31" s="59"/>
       <c r="V31" s="61"/>
     </row>
@@ -43262,13 +43206,13 @@
       <c r="M32" s="76"/>
       <c r="N32" s="76"/>
       <c r="O32" s="76"/>
-      <c r="P32" s="204" t="s">
+      <c r="P32" s="226" t="s">
         <v>122</v>
       </c>
-      <c r="Q32" s="205"/>
-      <c r="R32" s="205"/>
-      <c r="S32" s="205"/>
-      <c r="T32" s="206"/>
+      <c r="Q32" s="227"/>
+      <c r="R32" s="227"/>
+      <c r="S32" s="227"/>
+      <c r="T32" s="228"/>
       <c r="U32" s="59"/>
       <c r="V32" s="61"/>
     </row>
@@ -43290,13 +43234,13 @@
       <c r="M33" s="50"/>
       <c r="N33" s="50"/>
       <c r="O33" s="50"/>
-      <c r="P33" s="204" t="s">
+      <c r="P33" s="226" t="s">
         <v>124</v>
       </c>
-      <c r="Q33" s="205"/>
-      <c r="R33" s="205"/>
-      <c r="S33" s="205"/>
-      <c r="T33" s="206"/>
+      <c r="Q33" s="227"/>
+      <c r="R33" s="227"/>
+      <c r="S33" s="227"/>
+      <c r="T33" s="228"/>
       <c r="U33" s="38"/>
       <c r="V33" s="62"/>
     </row>
@@ -43318,13 +43262,13 @@
       <c r="M34" s="6"/>
       <c r="N34" s="6"/>
       <c r="O34" s="6"/>
-      <c r="P34" s="204" t="s">
+      <c r="P34" s="226" t="s">
         <v>125</v>
       </c>
-      <c r="Q34" s="205"/>
-      <c r="R34" s="205"/>
-      <c r="S34" s="205"/>
-      <c r="T34" s="206"/>
+      <c r="Q34" s="227"/>
+      <c r="R34" s="227"/>
+      <c r="S34" s="227"/>
+      <c r="T34" s="228"/>
       <c r="U34" s="69"/>
       <c r="V34" s="70"/>
     </row>
@@ -43346,13 +43290,13 @@
       <c r="M35" s="6"/>
       <c r="N35" s="6"/>
       <c r="O35" s="6"/>
-      <c r="P35" s="204" t="s">
+      <c r="P35" s="226" t="s">
         <v>126</v>
       </c>
-      <c r="Q35" s="205"/>
-      <c r="R35" s="205"/>
-      <c r="S35" s="205"/>
-      <c r="T35" s="206"/>
+      <c r="Q35" s="227"/>
+      <c r="R35" s="227"/>
+      <c r="S35" s="227"/>
+      <c r="T35" s="228"/>
       <c r="U35" s="69"/>
       <c r="V35" s="70"/>
     </row>
@@ -43376,11 +43320,11 @@
       <c r="M36" s="4"/>
       <c r="N36" s="4"/>
       <c r="O36" s="4"/>
-      <c r="P36" s="204"/>
-      <c r="Q36" s="205"/>
-      <c r="R36" s="205"/>
-      <c r="S36" s="205"/>
-      <c r="T36" s="206"/>
+      <c r="P36" s="226"/>
+      <c r="Q36" s="227"/>
+      <c r="R36" s="227"/>
+      <c r="S36" s="227"/>
+      <c r="T36" s="228"/>
       <c r="U36" s="14"/>
       <c r="V36" s="23"/>
     </row>
@@ -43402,13 +43346,13 @@
       <c r="M37" s="4"/>
       <c r="N37" s="4"/>
       <c r="O37" s="4"/>
-      <c r="P37" s="204" t="s">
+      <c r="P37" s="226" t="s">
         <v>127</v>
       </c>
-      <c r="Q37" s="205"/>
-      <c r="R37" s="205"/>
-      <c r="S37" s="205"/>
-      <c r="T37" s="206"/>
+      <c r="Q37" s="227"/>
+      <c r="R37" s="227"/>
+      <c r="S37" s="227"/>
+      <c r="T37" s="228"/>
       <c r="U37" s="14"/>
       <c r="V37" s="23"/>
     </row>
@@ -43430,13 +43374,13 @@
       <c r="M38" s="4"/>
       <c r="N38" s="4"/>
       <c r="O38" s="4"/>
-      <c r="P38" s="204" t="s">
+      <c r="P38" s="226" t="s">
         <v>128</v>
       </c>
-      <c r="Q38" s="205"/>
-      <c r="R38" s="205"/>
-      <c r="S38" s="205"/>
-      <c r="T38" s="206"/>
+      <c r="Q38" s="227"/>
+      <c r="R38" s="227"/>
+      <c r="S38" s="227"/>
+      <c r="T38" s="228"/>
       <c r="U38" s="14"/>
       <c r="V38" s="23"/>
     </row>
@@ -43460,11 +43404,11 @@
       <c r="M39" s="4"/>
       <c r="N39" s="4"/>
       <c r="O39" s="4"/>
-      <c r="P39" s="204"/>
-      <c r="Q39" s="205"/>
-      <c r="R39" s="205"/>
-      <c r="S39" s="205"/>
-      <c r="T39" s="206"/>
+      <c r="P39" s="226"/>
+      <c r="Q39" s="227"/>
+      <c r="R39" s="227"/>
+      <c r="S39" s="227"/>
+      <c r="T39" s="228"/>
       <c r="U39" s="14"/>
       <c r="V39" s="23"/>
     </row>
@@ -43488,11 +43432,11 @@
       <c r="M40" s="4"/>
       <c r="N40" s="4"/>
       <c r="O40" s="4"/>
-      <c r="P40" s="204"/>
-      <c r="Q40" s="205"/>
-      <c r="R40" s="205"/>
-      <c r="S40" s="205"/>
-      <c r="T40" s="206"/>
+      <c r="P40" s="226"/>
+      <c r="Q40" s="227"/>
+      <c r="R40" s="227"/>
+      <c r="S40" s="227"/>
+      <c r="T40" s="228"/>
       <c r="U40" s="14"/>
       <c r="V40" s="23"/>
     </row>
@@ -43514,13 +43458,13 @@
       <c r="M41" s="6"/>
       <c r="N41" s="6"/>
       <c r="O41" s="6"/>
-      <c r="P41" s="204" t="s">
+      <c r="P41" s="226" t="s">
         <v>138</v>
       </c>
-      <c r="Q41" s="205"/>
-      <c r="R41" s="205"/>
-      <c r="S41" s="205"/>
-      <c r="T41" s="206"/>
+      <c r="Q41" s="227"/>
+      <c r="R41" s="227"/>
+      <c r="S41" s="227"/>
+      <c r="T41" s="228"/>
       <c r="U41" s="69"/>
       <c r="V41" s="70"/>
     </row>
@@ -43542,13 +43486,13 @@
       <c r="M42" s="4"/>
       <c r="N42" s="4"/>
       <c r="O42" s="6"/>
-      <c r="P42" s="204" t="s">
+      <c r="P42" s="226" t="s">
         <v>129</v>
       </c>
-      <c r="Q42" s="205"/>
-      <c r="R42" s="205"/>
-      <c r="S42" s="205"/>
-      <c r="T42" s="206"/>
+      <c r="Q42" s="227"/>
+      <c r="R42" s="227"/>
+      <c r="S42" s="227"/>
+      <c r="T42" s="228"/>
       <c r="U42" s="14"/>
       <c r="V42" s="23"/>
     </row>
@@ -43570,13 +43514,13 @@
       <c r="M43" s="4"/>
       <c r="N43" s="4"/>
       <c r="O43" s="6"/>
-      <c r="P43" s="204" t="s">
+      <c r="P43" s="226" t="s">
         <v>130</v>
       </c>
-      <c r="Q43" s="205"/>
-      <c r="R43" s="205"/>
-      <c r="S43" s="205"/>
-      <c r="T43" s="206"/>
+      <c r="Q43" s="227"/>
+      <c r="R43" s="227"/>
+      <c r="S43" s="227"/>
+      <c r="T43" s="228"/>
       <c r="U43" s="14"/>
       <c r="V43" s="23"/>
     </row>
@@ -43600,13 +43544,13 @@
       <c r="M44" s="4"/>
       <c r="N44" s="4"/>
       <c r="O44" s="6"/>
-      <c r="P44" s="204" t="s">
+      <c r="P44" s="226" t="s">
         <v>131</v>
       </c>
-      <c r="Q44" s="205"/>
-      <c r="R44" s="205"/>
-      <c r="S44" s="205"/>
-      <c r="T44" s="206"/>
+      <c r="Q44" s="227"/>
+      <c r="R44" s="227"/>
+      <c r="S44" s="227"/>
+      <c r="T44" s="228"/>
       <c r="U44" s="14"/>
       <c r="V44" s="23"/>
     </row>
@@ -43630,13 +43574,13 @@
       <c r="M45" s="4"/>
       <c r="N45" s="4"/>
       <c r="O45" s="6"/>
-      <c r="P45" s="204" t="s">
+      <c r="P45" s="226" t="s">
         <v>135</v>
       </c>
-      <c r="Q45" s="205"/>
-      <c r="R45" s="205"/>
-      <c r="S45" s="205"/>
-      <c r="T45" s="206"/>
+      <c r="Q45" s="227"/>
+      <c r="R45" s="227"/>
+      <c r="S45" s="227"/>
+      <c r="T45" s="228"/>
       <c r="U45" s="14"/>
       <c r="V45" s="23"/>
     </row>
@@ -43660,13 +43604,13 @@
       <c r="M46" s="76"/>
       <c r="N46" s="76"/>
       <c r="O46" s="76"/>
-      <c r="P46" s="204" t="s">
+      <c r="P46" s="226" t="s">
         <v>132</v>
       </c>
-      <c r="Q46" s="205"/>
-      <c r="R46" s="205"/>
-      <c r="S46" s="205"/>
-      <c r="T46" s="206"/>
+      <c r="Q46" s="227"/>
+      <c r="R46" s="227"/>
+      <c r="S46" s="227"/>
+      <c r="T46" s="228"/>
       <c r="U46" s="59"/>
       <c r="V46" s="61"/>
     </row>
@@ -43690,13 +43634,13 @@
       <c r="M47" s="76"/>
       <c r="N47" s="76"/>
       <c r="O47" s="76"/>
-      <c r="P47" s="204" t="s">
+      <c r="P47" s="226" t="s">
         <v>133</v>
       </c>
-      <c r="Q47" s="205"/>
-      <c r="R47" s="205"/>
-      <c r="S47" s="205"/>
-      <c r="T47" s="206"/>
+      <c r="Q47" s="227"/>
+      <c r="R47" s="227"/>
+      <c r="S47" s="227"/>
+      <c r="T47" s="228"/>
       <c r="U47" s="59"/>
       <c r="V47" s="61"/>
     </row>
@@ -43720,13 +43664,13 @@
       <c r="M48" s="76"/>
       <c r="N48" s="76"/>
       <c r="O48" s="76"/>
-      <c r="P48" s="204" t="s">
+      <c r="P48" s="226" t="s">
         <v>134</v>
       </c>
-      <c r="Q48" s="205"/>
-      <c r="R48" s="205"/>
-      <c r="S48" s="205"/>
-      <c r="T48" s="206"/>
+      <c r="Q48" s="227"/>
+      <c r="R48" s="227"/>
+      <c r="S48" s="227"/>
+      <c r="T48" s="228"/>
       <c r="U48" s="59"/>
       <c r="V48" s="61"/>
     </row>
@@ -43750,13 +43694,13 @@
       <c r="M49" s="76"/>
       <c r="N49" s="76"/>
       <c r="O49" s="76"/>
-      <c r="P49" s="204" t="s">
+      <c r="P49" s="226" t="s">
         <v>136</v>
       </c>
-      <c r="Q49" s="205"/>
-      <c r="R49" s="205"/>
-      <c r="S49" s="205"/>
-      <c r="T49" s="206"/>
+      <c r="Q49" s="227"/>
+      <c r="R49" s="227"/>
+      <c r="S49" s="227"/>
+      <c r="T49" s="228"/>
       <c r="U49" s="59"/>
       <c r="V49" s="61"/>
     </row>
@@ -43780,11 +43724,11 @@
       <c r="M50" s="76"/>
       <c r="N50" s="76"/>
       <c r="O50" s="76"/>
-      <c r="P50" s="204"/>
-      <c r="Q50" s="205"/>
-      <c r="R50" s="205"/>
-      <c r="S50" s="205"/>
-      <c r="T50" s="206"/>
+      <c r="P50" s="226"/>
+      <c r="Q50" s="227"/>
+      <c r="R50" s="227"/>
+      <c r="S50" s="227"/>
+      <c r="T50" s="228"/>
       <c r="U50" s="59"/>
       <c r="V50" s="61"/>
     </row>
@@ -43808,11 +43752,11 @@
       <c r="M51" s="76"/>
       <c r="N51" s="76"/>
       <c r="O51" s="76"/>
-      <c r="P51" s="204"/>
-      <c r="Q51" s="205"/>
-      <c r="R51" s="205"/>
-      <c r="S51" s="205"/>
-      <c r="T51" s="206"/>
+      <c r="P51" s="226"/>
+      <c r="Q51" s="227"/>
+      <c r="R51" s="227"/>
+      <c r="S51" s="227"/>
+      <c r="T51" s="228"/>
       <c r="U51" s="59"/>
       <c r="V51" s="61"/>
     </row>
@@ -43836,11 +43780,11 @@
       <c r="M52" s="76"/>
       <c r="N52" s="76"/>
       <c r="O52" s="76"/>
-      <c r="P52" s="204"/>
-      <c r="Q52" s="205"/>
-      <c r="R52" s="205"/>
-      <c r="S52" s="205"/>
-      <c r="T52" s="206"/>
+      <c r="P52" s="226"/>
+      <c r="Q52" s="227"/>
+      <c r="R52" s="227"/>
+      <c r="S52" s="227"/>
+      <c r="T52" s="228"/>
       <c r="U52" s="59"/>
       <c r="V52" s="61"/>
     </row>
@@ -43869,64 +43813,64 @@
       <c r="V53" s="57"/>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A54" s="228" t="s">
+      <c r="A54" s="204" t="s">
         <v>120</v>
       </c>
-      <c r="B54" s="229"/>
-      <c r="C54" s="229"/>
-      <c r="D54" s="229"/>
-      <c r="E54" s="229"/>
-      <c r="F54" s="229"/>
-      <c r="G54" s="230"/>
-      <c r="H54" s="228" t="s">
+      <c r="B54" s="205"/>
+      <c r="C54" s="205"/>
+      <c r="D54" s="205"/>
+      <c r="E54" s="205"/>
+      <c r="F54" s="205"/>
+      <c r="G54" s="206"/>
+      <c r="H54" s="204" t="s">
         <v>121</v>
       </c>
-      <c r="I54" s="229"/>
-      <c r="J54" s="229"/>
-      <c r="K54" s="229"/>
-      <c r="L54" s="229"/>
-      <c r="M54" s="229"/>
-      <c r="N54" s="230"/>
-      <c r="O54" s="228" t="s">
+      <c r="I54" s="205"/>
+      <c r="J54" s="205"/>
+      <c r="K54" s="205"/>
+      <c r="L54" s="205"/>
+      <c r="M54" s="205"/>
+      <c r="N54" s="206"/>
+      <c r="O54" s="204" t="s">
         <v>121</v>
       </c>
-      <c r="P54" s="229"/>
-      <c r="Q54" s="229"/>
-      <c r="R54" s="229"/>
-      <c r="S54" s="229"/>
-      <c r="T54" s="229"/>
-      <c r="U54" s="229"/>
-      <c r="V54" s="230"/>
+      <c r="P54" s="205"/>
+      <c r="Q54" s="205"/>
+      <c r="R54" s="205"/>
+      <c r="S54" s="205"/>
+      <c r="T54" s="205"/>
+      <c r="U54" s="205"/>
+      <c r="V54" s="206"/>
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A55" s="210" t="s">
+      <c r="A55" s="207" t="s">
         <v>86</v>
       </c>
-      <c r="B55" s="211"/>
-      <c r="C55" s="211"/>
-      <c r="D55" s="211"/>
-      <c r="E55" s="211"/>
-      <c r="F55" s="211"/>
-      <c r="G55" s="212"/>
-      <c r="H55" s="210" t="s">
+      <c r="B55" s="208"/>
+      <c r="C55" s="208"/>
+      <c r="D55" s="208"/>
+      <c r="E55" s="208"/>
+      <c r="F55" s="208"/>
+      <c r="G55" s="209"/>
+      <c r="H55" s="207" t="s">
         <v>90</v>
       </c>
-      <c r="I55" s="211"/>
-      <c r="J55" s="211"/>
-      <c r="K55" s="211"/>
-      <c r="L55" s="211"/>
-      <c r="M55" s="211"/>
-      <c r="N55" s="212"/>
-      <c r="O55" s="210" t="s">
+      <c r="I55" s="208"/>
+      <c r="J55" s="208"/>
+      <c r="K55" s="208"/>
+      <c r="L55" s="208"/>
+      <c r="M55" s="208"/>
+      <c r="N55" s="209"/>
+      <c r="O55" s="207" t="s">
         <v>91</v>
       </c>
-      <c r="P55" s="211"/>
-      <c r="Q55" s="211"/>
-      <c r="R55" s="211"/>
-      <c r="S55" s="211"/>
-      <c r="T55" s="211"/>
-      <c r="U55" s="211"/>
-      <c r="V55" s="212"/>
+      <c r="P55" s="208"/>
+      <c r="Q55" s="208"/>
+      <c r="R55" s="208"/>
+      <c r="S55" s="208"/>
+      <c r="T55" s="208"/>
+      <c r="U55" s="208"/>
+      <c r="V55" s="209"/>
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A56" s="44"/>
@@ -44095,32 +44039,32 @@
       <c r="D62" s="40">
         <v>2</v>
       </c>
-      <c r="E62" s="213" t="s">
+      <c r="E62" s="236" t="s">
         <v>85</v>
       </c>
-      <c r="F62" s="214"/>
-      <c r="G62" s="214"/>
-      <c r="H62" s="214"/>
-      <c r="I62" s="214"/>
-      <c r="J62" s="214"/>
-      <c r="K62" s="214"/>
-      <c r="L62" s="214"/>
-      <c r="M62" s="214"/>
-      <c r="N62" s="214"/>
-      <c r="O62" s="214"/>
-      <c r="P62" s="214"/>
-      <c r="Q62" s="215"/>
-      <c r="R62" s="216" t="s">
+      <c r="F62" s="237"/>
+      <c r="G62" s="237"/>
+      <c r="H62" s="237"/>
+      <c r="I62" s="237"/>
+      <c r="J62" s="237"/>
+      <c r="K62" s="237"/>
+      <c r="L62" s="237"/>
+      <c r="M62" s="237"/>
+      <c r="N62" s="237"/>
+      <c r="O62" s="237"/>
+      <c r="P62" s="237"/>
+      <c r="Q62" s="238"/>
+      <c r="R62" s="239" t="s">
         <v>83</v>
       </c>
-      <c r="S62" s="217"/>
-      <c r="T62" s="217">
+      <c r="S62" s="240"/>
+      <c r="T62" s="240">
         <v>1</v>
       </c>
-      <c r="U62" s="220" t="s">
+      <c r="U62" s="243" t="s">
         <v>84</v>
       </c>
-      <c r="V62" s="222">
+      <c r="V62" s="245">
         <v>2</v>
       </c>
     </row>
@@ -44144,21 +44088,21 @@
       <c r="I63" s="26"/>
       <c r="J63" s="26"/>
       <c r="K63" s="28"/>
-      <c r="L63" s="224" t="s">
+      <c r="L63" s="247" t="s">
         <v>82</v>
       </c>
-      <c r="M63" s="225"/>
-      <c r="N63" s="225"/>
-      <c r="O63" s="225"/>
-      <c r="P63" s="226">
+      <c r="M63" s="248"/>
+      <c r="N63" s="248"/>
+      <c r="O63" s="248"/>
+      <c r="P63" s="249">
         <v>39660</v>
       </c>
-      <c r="Q63" s="227"/>
-      <c r="R63" s="218"/>
-      <c r="S63" s="219"/>
-      <c r="T63" s="219"/>
-      <c r="U63" s="221"/>
-      <c r="V63" s="223"/>
+      <c r="Q63" s="250"/>
+      <c r="R63" s="241"/>
+      <c r="S63" s="242"/>
+      <c r="T63" s="242"/>
+      <c r="U63" s="244"/>
+      <c r="V63" s="246"/>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A64" s="53"/>
@@ -44210,6 +44154,44 @@
     </row>
   </sheetData>
   <mergeCells count="54">
+    <mergeCell ref="P33:T33"/>
+    <mergeCell ref="P52:T52"/>
+    <mergeCell ref="C20:L20"/>
+    <mergeCell ref="P46:T46"/>
+    <mergeCell ref="P47:T47"/>
+    <mergeCell ref="P48:T48"/>
+    <mergeCell ref="P49:T49"/>
+    <mergeCell ref="P50:T50"/>
+    <mergeCell ref="P51:T51"/>
+    <mergeCell ref="P40:T40"/>
+    <mergeCell ref="P41:T41"/>
+    <mergeCell ref="P42:T42"/>
+    <mergeCell ref="P43:T43"/>
+    <mergeCell ref="P44:T44"/>
+    <mergeCell ref="P45:T45"/>
+    <mergeCell ref="H55:N55"/>
+    <mergeCell ref="O55:V55"/>
+    <mergeCell ref="P22:T22"/>
+    <mergeCell ref="P23:T23"/>
+    <mergeCell ref="P24:T24"/>
+    <mergeCell ref="P25:T25"/>
+    <mergeCell ref="P26:T26"/>
+    <mergeCell ref="P36:T36"/>
+    <mergeCell ref="P37:T37"/>
+    <mergeCell ref="P38:T38"/>
+    <mergeCell ref="P39:T39"/>
+    <mergeCell ref="P28:T28"/>
+    <mergeCell ref="P29:T29"/>
+    <mergeCell ref="P30:T30"/>
+    <mergeCell ref="P31:T31"/>
+    <mergeCell ref="P35:T35"/>
+    <mergeCell ref="E62:Q62"/>
+    <mergeCell ref="R62:S63"/>
+    <mergeCell ref="T62:T63"/>
+    <mergeCell ref="U62:U63"/>
+    <mergeCell ref="V62:V63"/>
+    <mergeCell ref="L63:O63"/>
+    <mergeCell ref="P63:Q63"/>
     <mergeCell ref="A54:G54"/>
     <mergeCell ref="H54:N54"/>
     <mergeCell ref="O54:V54"/>
@@ -44226,44 +44208,6 @@
     <mergeCell ref="P20:T21"/>
     <mergeCell ref="P27:T27"/>
     <mergeCell ref="P34:T34"/>
-    <mergeCell ref="E62:Q62"/>
-    <mergeCell ref="R62:S63"/>
-    <mergeCell ref="T62:T63"/>
-    <mergeCell ref="U62:U63"/>
-    <mergeCell ref="V62:V63"/>
-    <mergeCell ref="L63:O63"/>
-    <mergeCell ref="P63:Q63"/>
-    <mergeCell ref="H55:N55"/>
-    <mergeCell ref="O55:V55"/>
-    <mergeCell ref="P22:T22"/>
-    <mergeCell ref="P23:T23"/>
-    <mergeCell ref="P24:T24"/>
-    <mergeCell ref="P25:T25"/>
-    <mergeCell ref="P26:T26"/>
-    <mergeCell ref="P36:T36"/>
-    <mergeCell ref="P37:T37"/>
-    <mergeCell ref="P38:T38"/>
-    <mergeCell ref="P39:T39"/>
-    <mergeCell ref="P28:T28"/>
-    <mergeCell ref="P29:T29"/>
-    <mergeCell ref="P30:T30"/>
-    <mergeCell ref="P31:T31"/>
-    <mergeCell ref="P35:T35"/>
-    <mergeCell ref="P33:T33"/>
-    <mergeCell ref="P52:T52"/>
-    <mergeCell ref="C20:L20"/>
-    <mergeCell ref="P46:T46"/>
-    <mergeCell ref="P47:T47"/>
-    <mergeCell ref="P48:T48"/>
-    <mergeCell ref="P49:T49"/>
-    <mergeCell ref="P50:T50"/>
-    <mergeCell ref="P51:T51"/>
-    <mergeCell ref="P40:T40"/>
-    <mergeCell ref="P41:T41"/>
-    <mergeCell ref="P42:T42"/>
-    <mergeCell ref="P43:T43"/>
-    <mergeCell ref="P44:T44"/>
-    <mergeCell ref="P45:T45"/>
   </mergeCells>
   <pageMargins left="1.4960629921259843" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="71" orientation="portrait" r:id="rId1"/>
@@ -44297,7 +44241,7 @@
       <c r="B2" s="81"/>
       <c r="C2" s="81"/>
       <c r="D2" s="193" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E2" s="193"/>
       <c r="F2" s="193"/>
@@ -44327,9 +44271,9 @@
       <c r="C4" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="D4" s="83" t="str">
-        <f>'MASTER '!F5</f>
-        <v>24TS09B310</v>
+      <c r="D4" s="83">
+        <f>MASTER!F5</f>
+        <v>0</v>
       </c>
       <c r="E4" s="77"/>
       <c r="F4" s="77"/>
@@ -44345,9 +44289,9 @@
       <c r="C5" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="D5" s="77" t="str">
-        <f>'MASTER '!F7</f>
-        <v>Gempol Ragas</v>
+      <c r="D5" s="77">
+        <f>MASTER!F7</f>
+        <v>0</v>
       </c>
       <c r="E5" s="78"/>
       <c r="F5" s="78"/>
@@ -44393,7 +44337,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="194" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B9" s="194"/>
       <c r="C9" s="194"/>
@@ -44868,7 +44812,7 @@
       <c r="I3" s="79"/>
       <c r="J3" s="79"/>
       <c r="M3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -44879,9 +44823,9 @@
       <c r="C4" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="D4" s="83" t="str">
-        <f>'MASTER '!F5</f>
-        <v>24TS09B310</v>
+      <c r="D4" s="83">
+        <f>MASTER!F5</f>
+        <v>0</v>
       </c>
       <c r="E4" s="77"/>
       <c r="F4" s="77"/>
@@ -44897,9 +44841,9 @@
       <c r="C5" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="D5" s="77" t="str">
-        <f>'MASTER '!F7</f>
-        <v>Gempol Ragas</v>
+      <c r="D5" s="77">
+        <f>MASTER!F7</f>
+        <v>0</v>
       </c>
       <c r="E5" s="78"/>
       <c r="F5" s="78"/>
@@ -44915,9 +44859,9 @@
       <c r="C6" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="D6" s="77" t="str">
-        <f>'MASTER '!F11</f>
-        <v xml:space="preserve">TSEL </v>
+      <c r="D6" s="77">
+        <f>MASTER!F11</f>
+        <v>0</v>
       </c>
       <c r="E6" s="78"/>
       <c r="F6" s="78"/>
@@ -44945,7 +44889,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="194" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B9" s="194"/>
       <c r="C9" s="194"/>
@@ -44973,158 +44917,158 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="198"/>
-      <c r="B11" s="316"/>
-      <c r="C11" s="316"/>
-      <c r="D11" s="316"/>
+      <c r="B11" s="199"/>
+      <c r="C11" s="199"/>
+      <c r="D11" s="199"/>
       <c r="E11" s="200"/>
       <c r="G11" s="198"/>
-      <c r="H11" s="316"/>
-      <c r="I11" s="316"/>
-      <c r="J11" s="316"/>
+      <c r="H11" s="199"/>
+      <c r="I11" s="199"/>
+      <c r="J11" s="199"/>
       <c r="K11" s="200"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="198"/>
-      <c r="B12" s="316"/>
-      <c r="C12" s="316"/>
-      <c r="D12" s="316"/>
+      <c r="B12" s="199"/>
+      <c r="C12" s="199"/>
+      <c r="D12" s="199"/>
       <c r="E12" s="200"/>
       <c r="G12" s="198"/>
-      <c r="H12" s="316"/>
-      <c r="I12" s="316"/>
-      <c r="J12" s="316"/>
+      <c r="H12" s="199"/>
+      <c r="I12" s="199"/>
+      <c r="J12" s="199"/>
       <c r="K12" s="200"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="198"/>
-      <c r="B13" s="316"/>
-      <c r="C13" s="316"/>
-      <c r="D13" s="316"/>
+      <c r="B13" s="199"/>
+      <c r="C13" s="199"/>
+      <c r="D13" s="199"/>
       <c r="E13" s="200"/>
       <c r="G13" s="198"/>
-      <c r="H13" s="316"/>
-      <c r="I13" s="316"/>
-      <c r="J13" s="316"/>
+      <c r="H13" s="199"/>
+      <c r="I13" s="199"/>
+      <c r="J13" s="199"/>
       <c r="K13" s="200"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="198"/>
-      <c r="B14" s="316"/>
-      <c r="C14" s="316"/>
-      <c r="D14" s="316"/>
+      <c r="B14" s="199"/>
+      <c r="C14" s="199"/>
+      <c r="D14" s="199"/>
       <c r="E14" s="200"/>
       <c r="G14" s="198"/>
-      <c r="H14" s="316"/>
-      <c r="I14" s="316"/>
-      <c r="J14" s="316"/>
+      <c r="H14" s="199"/>
+      <c r="I14" s="199"/>
+      <c r="J14" s="199"/>
       <c r="K14" s="200"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="198"/>
-      <c r="B15" s="316"/>
-      <c r="C15" s="316"/>
-      <c r="D15" s="316"/>
+      <c r="B15" s="199"/>
+      <c r="C15" s="199"/>
+      <c r="D15" s="199"/>
       <c r="E15" s="200"/>
       <c r="G15" s="198"/>
-      <c r="H15" s="316"/>
-      <c r="I15" s="316"/>
-      <c r="J15" s="316"/>
+      <c r="H15" s="199"/>
+      <c r="I15" s="199"/>
+      <c r="J15" s="199"/>
       <c r="K15" s="200"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="198"/>
-      <c r="B16" s="316"/>
-      <c r="C16" s="316"/>
-      <c r="D16" s="316"/>
+      <c r="B16" s="199"/>
+      <c r="C16" s="199"/>
+      <c r="D16" s="199"/>
       <c r="E16" s="200"/>
       <c r="G16" s="198"/>
-      <c r="H16" s="316"/>
-      <c r="I16" s="316"/>
-      <c r="J16" s="316"/>
+      <c r="H16" s="199"/>
+      <c r="I16" s="199"/>
+      <c r="J16" s="199"/>
       <c r="K16" s="200"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="198"/>
-      <c r="B17" s="316"/>
-      <c r="C17" s="316"/>
-      <c r="D17" s="316"/>
+      <c r="B17" s="199"/>
+      <c r="C17" s="199"/>
+      <c r="D17" s="199"/>
       <c r="E17" s="200"/>
       <c r="G17" s="198"/>
-      <c r="H17" s="316"/>
-      <c r="I17" s="316"/>
-      <c r="J17" s="316"/>
+      <c r="H17" s="199"/>
+      <c r="I17" s="199"/>
+      <c r="J17" s="199"/>
       <c r="K17" s="200"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="198"/>
-      <c r="B18" s="316"/>
-      <c r="C18" s="316"/>
-      <c r="D18" s="316"/>
+      <c r="B18" s="199"/>
+      <c r="C18" s="199"/>
+      <c r="D18" s="199"/>
       <c r="E18" s="200"/>
       <c r="G18" s="198"/>
-      <c r="H18" s="316"/>
-      <c r="I18" s="316"/>
-      <c r="J18" s="316"/>
+      <c r="H18" s="199"/>
+      <c r="I18" s="199"/>
+      <c r="J18" s="199"/>
       <c r="K18" s="200"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="198"/>
-      <c r="B19" s="316"/>
-      <c r="C19" s="316"/>
-      <c r="D19" s="316"/>
+      <c r="B19" s="199"/>
+      <c r="C19" s="199"/>
+      <c r="D19" s="199"/>
       <c r="E19" s="200"/>
       <c r="G19" s="198"/>
-      <c r="H19" s="316"/>
-      <c r="I19" s="316"/>
-      <c r="J19" s="316"/>
+      <c r="H19" s="199"/>
+      <c r="I19" s="199"/>
+      <c r="J19" s="199"/>
       <c r="K19" s="200"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="198"/>
-      <c r="B20" s="316"/>
-      <c r="C20" s="316"/>
-      <c r="D20" s="316"/>
+      <c r="B20" s="199"/>
+      <c r="C20" s="199"/>
+      <c r="D20" s="199"/>
       <c r="E20" s="200"/>
       <c r="G20" s="198"/>
-      <c r="H20" s="316"/>
-      <c r="I20" s="316"/>
-      <c r="J20" s="316"/>
+      <c r="H20" s="199"/>
+      <c r="I20" s="199"/>
+      <c r="J20" s="199"/>
       <c r="K20" s="200"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="198"/>
-      <c r="B21" s="316"/>
-      <c r="C21" s="316"/>
-      <c r="D21" s="316"/>
+      <c r="B21" s="199"/>
+      <c r="C21" s="199"/>
+      <c r="D21" s="199"/>
       <c r="E21" s="200"/>
       <c r="G21" s="198"/>
-      <c r="H21" s="316"/>
-      <c r="I21" s="316"/>
-      <c r="J21" s="316"/>
+      <c r="H21" s="199"/>
+      <c r="I21" s="199"/>
+      <c r="J21" s="199"/>
       <c r="K21" s="200"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="198"/>
-      <c r="B22" s="316"/>
-      <c r="C22" s="316"/>
-      <c r="D22" s="316"/>
+      <c r="B22" s="199"/>
+      <c r="C22" s="199"/>
+      <c r="D22" s="199"/>
       <c r="E22" s="200"/>
       <c r="G22" s="198"/>
-      <c r="H22" s="316"/>
-      <c r="I22" s="316"/>
-      <c r="J22" s="316"/>
+      <c r="H22" s="199"/>
+      <c r="I22" s="199"/>
+      <c r="J22" s="199"/>
       <c r="K22" s="200"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="198"/>
-      <c r="B23" s="316"/>
-      <c r="C23" s="316"/>
-      <c r="D23" s="316"/>
+      <c r="B23" s="199"/>
+      <c r="C23" s="199"/>
+      <c r="D23" s="199"/>
       <c r="E23" s="200"/>
       <c r="G23" s="198"/>
-      <c r="H23" s="316"/>
-      <c r="I23" s="316"/>
-      <c r="J23" s="316"/>
+      <c r="H23" s="199"/>
+      <c r="I23" s="199"/>
+      <c r="J23" s="199"/>
       <c r="K23" s="200"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -45401,16 +45345,16 @@
     <row r="2" spans="1:11" ht="23.25" x14ac:dyDescent="0.35">
       <c r="B2" s="81"/>
       <c r="C2" s="81"/>
-      <c r="D2" s="313" t="s">
+      <c r="D2" s="304" t="s">
         <v>196</v>
       </c>
-      <c r="E2" s="313"/>
-      <c r="F2" s="313"/>
-      <c r="G2" s="313"/>
-      <c r="H2" s="313"/>
-      <c r="I2" s="313"/>
-      <c r="J2" s="313"/>
-      <c r="K2" s="313"/>
+      <c r="E2" s="304"/>
+      <c r="F2" s="304"/>
+      <c r="G2" s="304"/>
+      <c r="H2" s="304"/>
+      <c r="I2" s="304"/>
+      <c r="J2" s="304"/>
+      <c r="K2" s="304"/>
     </row>
     <row r="3" spans="1:11" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A3" s="79"/>
@@ -45432,9 +45376,9 @@
       <c r="C4" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="D4" s="83" t="str">
+      <c r="D4" s="83">
         <f>SKOM!D4</f>
-        <v>24TS09B310</v>
+        <v>0</v>
       </c>
       <c r="E4" s="77"/>
       <c r="F4" s="77"/>
@@ -45450,9 +45394,9 @@
       <c r="C5" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="D5" s="77" t="str">
+      <c r="D5" s="77">
         <f>SKOM!D5</f>
-        <v>Gempol Ragas</v>
+        <v>0</v>
       </c>
       <c r="E5" s="78"/>
       <c r="F5" s="78"/>
@@ -45468,9 +45412,9 @@
       <c r="C6" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="D6" s="77" t="str">
+      <c r="D6" s="77">
         <f>SKOM!D6</f>
-        <v xml:space="preserve">TSEL </v>
+        <v>0</v>
       </c>
       <c r="E6" s="78"/>
       <c r="F6" s="78"/>
@@ -45498,14 +45442,14 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="194" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="B9" s="194"/>
       <c r="C9" s="194"/>
       <c r="D9" s="194"/>
       <c r="E9" s="194"/>
       <c r="G9" s="194" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="H9" s="194"/>
       <c r="I9" s="194"/>
@@ -45513,11 +45457,11 @@
       <c r="K9" s="194"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="234"/>
-      <c r="B10" s="235"/>
-      <c r="C10" s="235"/>
-      <c r="D10" s="235"/>
-      <c r="E10" s="236"/>
+      <c r="A10" s="213"/>
+      <c r="B10" s="214"/>
+      <c r="C10" s="214"/>
+      <c r="D10" s="214"/>
+      <c r="E10" s="215"/>
       <c r="G10" s="195"/>
       <c r="H10" s="196"/>
       <c r="I10" s="196"/>
@@ -45525,11 +45469,11 @@
       <c r="K10" s="197"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="237"/>
-      <c r="B11" s="238"/>
-      <c r="C11" s="238"/>
-      <c r="D11" s="238"/>
-      <c r="E11" s="239"/>
+      <c r="A11" s="216"/>
+      <c r="B11" s="217"/>
+      <c r="C11" s="217"/>
+      <c r="D11" s="217"/>
+      <c r="E11" s="218"/>
       <c r="G11" s="198"/>
       <c r="H11" s="199"/>
       <c r="I11" s="199"/>
@@ -45537,11 +45481,11 @@
       <c r="K11" s="200"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="237"/>
-      <c r="B12" s="238"/>
-      <c r="C12" s="238"/>
-      <c r="D12" s="238"/>
-      <c r="E12" s="239"/>
+      <c r="A12" s="216"/>
+      <c r="B12" s="217"/>
+      <c r="C12" s="217"/>
+      <c r="D12" s="217"/>
+      <c r="E12" s="218"/>
       <c r="G12" s="198"/>
       <c r="H12" s="199"/>
       <c r="I12" s="199"/>
@@ -45549,11 +45493,11 @@
       <c r="K12" s="200"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="237"/>
-      <c r="B13" s="238"/>
-      <c r="C13" s="238"/>
-      <c r="D13" s="238"/>
-      <c r="E13" s="239"/>
+      <c r="A13" s="216"/>
+      <c r="B13" s="217"/>
+      <c r="C13" s="217"/>
+      <c r="D13" s="217"/>
+      <c r="E13" s="218"/>
       <c r="G13" s="198"/>
       <c r="H13" s="199"/>
       <c r="I13" s="199"/>
@@ -45561,11 +45505,11 @@
       <c r="K13" s="200"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="237"/>
-      <c r="B14" s="238"/>
-      <c r="C14" s="238"/>
-      <c r="D14" s="238"/>
-      <c r="E14" s="239"/>
+      <c r="A14" s="216"/>
+      <c r="B14" s="217"/>
+      <c r="C14" s="217"/>
+      <c r="D14" s="217"/>
+      <c r="E14" s="218"/>
       <c r="G14" s="198"/>
       <c r="H14" s="199"/>
       <c r="I14" s="199"/>
@@ -45573,11 +45517,11 @@
       <c r="K14" s="200"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="237"/>
-      <c r="B15" s="238"/>
-      <c r="C15" s="238"/>
-      <c r="D15" s="238"/>
-      <c r="E15" s="239"/>
+      <c r="A15" s="216"/>
+      <c r="B15" s="217"/>
+      <c r="C15" s="217"/>
+      <c r="D15" s="217"/>
+      <c r="E15" s="218"/>
       <c r="G15" s="198"/>
       <c r="H15" s="199"/>
       <c r="I15" s="199"/>
@@ -45585,11 +45529,11 @@
       <c r="K15" s="200"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="237"/>
-      <c r="B16" s="238"/>
-      <c r="C16" s="238"/>
-      <c r="D16" s="238"/>
-      <c r="E16" s="239"/>
+      <c r="A16" s="216"/>
+      <c r="B16" s="217"/>
+      <c r="C16" s="217"/>
+      <c r="D16" s="217"/>
+      <c r="E16" s="218"/>
       <c r="G16" s="198"/>
       <c r="H16" s="199"/>
       <c r="I16" s="199"/>
@@ -45597,11 +45541,11 @@
       <c r="K16" s="200"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="237"/>
-      <c r="B17" s="238"/>
-      <c r="C17" s="238"/>
-      <c r="D17" s="238"/>
-      <c r="E17" s="239"/>
+      <c r="A17" s="216"/>
+      <c r="B17" s="217"/>
+      <c r="C17" s="217"/>
+      <c r="D17" s="217"/>
+      <c r="E17" s="218"/>
       <c r="G17" s="198"/>
       <c r="H17" s="199"/>
       <c r="I17" s="199"/>
@@ -45609,11 +45553,11 @@
       <c r="K17" s="200"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="237"/>
-      <c r="B18" s="238"/>
-      <c r="C18" s="238"/>
-      <c r="D18" s="238"/>
-      <c r="E18" s="239"/>
+      <c r="A18" s="216"/>
+      <c r="B18" s="217"/>
+      <c r="C18" s="217"/>
+      <c r="D18" s="217"/>
+      <c r="E18" s="218"/>
       <c r="G18" s="198"/>
       <c r="H18" s="199"/>
       <c r="I18" s="199"/>
@@ -45621,11 +45565,11 @@
       <c r="K18" s="200"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="237"/>
-      <c r="B19" s="238"/>
-      <c r="C19" s="238"/>
-      <c r="D19" s="238"/>
-      <c r="E19" s="239"/>
+      <c r="A19" s="216"/>
+      <c r="B19" s="217"/>
+      <c r="C19" s="217"/>
+      <c r="D19" s="217"/>
+      <c r="E19" s="218"/>
       <c r="G19" s="198"/>
       <c r="H19" s="199"/>
       <c r="I19" s="199"/>
@@ -45633,11 +45577,11 @@
       <c r="K19" s="200"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="237"/>
-      <c r="B20" s="238"/>
-      <c r="C20" s="238"/>
-      <c r="D20" s="238"/>
-      <c r="E20" s="239"/>
+      <c r="A20" s="216"/>
+      <c r="B20" s="217"/>
+      <c r="C20" s="217"/>
+      <c r="D20" s="217"/>
+      <c r="E20" s="218"/>
       <c r="G20" s="198"/>
       <c r="H20" s="199"/>
       <c r="I20" s="199"/>
@@ -45645,11 +45589,11 @@
       <c r="K20" s="200"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="237"/>
-      <c r="B21" s="238"/>
-      <c r="C21" s="238"/>
-      <c r="D21" s="238"/>
-      <c r="E21" s="239"/>
+      <c r="A21" s="216"/>
+      <c r="B21" s="217"/>
+      <c r="C21" s="217"/>
+      <c r="D21" s="217"/>
+      <c r="E21" s="218"/>
       <c r="G21" s="198"/>
       <c r="H21" s="199"/>
       <c r="I21" s="199"/>
@@ -45657,11 +45601,11 @@
       <c r="K21" s="200"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="237"/>
-      <c r="B22" s="238"/>
-      <c r="C22" s="238"/>
-      <c r="D22" s="238"/>
-      <c r="E22" s="239"/>
+      <c r="A22" s="216"/>
+      <c r="B22" s="217"/>
+      <c r="C22" s="217"/>
+      <c r="D22" s="217"/>
+      <c r="E22" s="218"/>
       <c r="G22" s="198"/>
       <c r="H22" s="199"/>
       <c r="I22" s="199"/>
@@ -45669,11 +45613,11 @@
       <c r="K22" s="200"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="237"/>
-      <c r="B23" s="238"/>
-      <c r="C23" s="238"/>
-      <c r="D23" s="238"/>
-      <c r="E23" s="239"/>
+      <c r="A23" s="216"/>
+      <c r="B23" s="217"/>
+      <c r="C23" s="217"/>
+      <c r="D23" s="217"/>
+      <c r="E23" s="218"/>
       <c r="G23" s="198"/>
       <c r="H23" s="199"/>
       <c r="I23" s="199"/>
@@ -45681,11 +45625,11 @@
       <c r="K23" s="200"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="240"/>
-      <c r="B24" s="241"/>
-      <c r="C24" s="241"/>
-      <c r="D24" s="241"/>
-      <c r="E24" s="242"/>
+      <c r="A24" s="219"/>
+      <c r="B24" s="220"/>
+      <c r="C24" s="220"/>
+      <c r="D24" s="220"/>
+      <c r="E24" s="221"/>
       <c r="G24" s="201"/>
       <c r="H24" s="202"/>
       <c r="I24" s="202"/>
@@ -45694,14 +45638,14 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="194" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="B26" s="194"/>
       <c r="C26" s="194"/>
       <c r="D26" s="194"/>
       <c r="E26" s="194"/>
       <c r="G26" s="194" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="H26" s="194"/>
       <c r="I26" s="194"/>
@@ -45714,11 +45658,11 @@
       <c r="C27" s="196"/>
       <c r="D27" s="196"/>
       <c r="E27" s="197"/>
-      <c r="G27" s="304"/>
-      <c r="H27" s="305"/>
-      <c r="I27" s="305"/>
-      <c r="J27" s="305"/>
-      <c r="K27" s="306"/>
+      <c r="G27" s="305"/>
+      <c r="H27" s="306"/>
+      <c r="I27" s="306"/>
+      <c r="J27" s="306"/>
+      <c r="K27" s="307"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="198"/>
@@ -45726,11 +45670,11 @@
       <c r="C28" s="199"/>
       <c r="D28" s="199"/>
       <c r="E28" s="200"/>
-      <c r="G28" s="307"/>
-      <c r="H28" s="308"/>
-      <c r="I28" s="308"/>
-      <c r="J28" s="308"/>
-      <c r="K28" s="309"/>
+      <c r="G28" s="308"/>
+      <c r="H28" s="309"/>
+      <c r="I28" s="309"/>
+      <c r="J28" s="309"/>
+      <c r="K28" s="310"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="198"/>
@@ -45738,11 +45682,11 @@
       <c r="C29" s="199"/>
       <c r="D29" s="199"/>
       <c r="E29" s="200"/>
-      <c r="G29" s="307"/>
-      <c r="H29" s="308"/>
-      <c r="I29" s="308"/>
-      <c r="J29" s="308"/>
-      <c r="K29" s="309"/>
+      <c r="G29" s="308"/>
+      <c r="H29" s="309"/>
+      <c r="I29" s="309"/>
+      <c r="J29" s="309"/>
+      <c r="K29" s="310"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="198"/>
@@ -45750,11 +45694,11 @@
       <c r="C30" s="199"/>
       <c r="D30" s="199"/>
       <c r="E30" s="200"/>
-      <c r="G30" s="307"/>
-      <c r="H30" s="308"/>
-      <c r="I30" s="308"/>
-      <c r="J30" s="308"/>
-      <c r="K30" s="309"/>
+      <c r="G30" s="308"/>
+      <c r="H30" s="309"/>
+      <c r="I30" s="309"/>
+      <c r="J30" s="309"/>
+      <c r="K30" s="310"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="198"/>
@@ -45762,11 +45706,11 @@
       <c r="C31" s="199"/>
       <c r="D31" s="199"/>
       <c r="E31" s="200"/>
-      <c r="G31" s="307"/>
-      <c r="H31" s="308"/>
-      <c r="I31" s="308"/>
-      <c r="J31" s="308"/>
-      <c r="K31" s="309"/>
+      <c r="G31" s="308"/>
+      <c r="H31" s="309"/>
+      <c r="I31" s="309"/>
+      <c r="J31" s="309"/>
+      <c r="K31" s="310"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="198"/>
@@ -45774,11 +45718,11 @@
       <c r="C32" s="199"/>
       <c r="D32" s="199"/>
       <c r="E32" s="200"/>
-      <c r="G32" s="307"/>
-      <c r="H32" s="308"/>
-      <c r="I32" s="308"/>
-      <c r="J32" s="308"/>
-      <c r="K32" s="309"/>
+      <c r="G32" s="308"/>
+      <c r="H32" s="309"/>
+      <c r="I32" s="309"/>
+      <c r="J32" s="309"/>
+      <c r="K32" s="310"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="198"/>
@@ -45786,11 +45730,11 @@
       <c r="C33" s="199"/>
       <c r="D33" s="199"/>
       <c r="E33" s="200"/>
-      <c r="G33" s="307"/>
-      <c r="H33" s="308"/>
-      <c r="I33" s="308"/>
-      <c r="J33" s="308"/>
-      <c r="K33" s="309"/>
+      <c r="G33" s="308"/>
+      <c r="H33" s="309"/>
+      <c r="I33" s="309"/>
+      <c r="J33" s="309"/>
+      <c r="K33" s="310"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="198"/>
@@ -45798,11 +45742,11 @@
       <c r="C34" s="199"/>
       <c r="D34" s="199"/>
       <c r="E34" s="200"/>
-      <c r="G34" s="307"/>
-      <c r="H34" s="308"/>
-      <c r="I34" s="308"/>
-      <c r="J34" s="308"/>
-      <c r="K34" s="309"/>
+      <c r="G34" s="308"/>
+      <c r="H34" s="309"/>
+      <c r="I34" s="309"/>
+      <c r="J34" s="309"/>
+      <c r="K34" s="310"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="198"/>
@@ -45810,11 +45754,11 @@
       <c r="C35" s="199"/>
       <c r="D35" s="199"/>
       <c r="E35" s="200"/>
-      <c r="G35" s="307"/>
-      <c r="H35" s="308"/>
-      <c r="I35" s="308"/>
-      <c r="J35" s="308"/>
-      <c r="K35" s="309"/>
+      <c r="G35" s="308"/>
+      <c r="H35" s="309"/>
+      <c r="I35" s="309"/>
+      <c r="J35" s="309"/>
+      <c r="K35" s="310"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="198"/>
@@ -45822,11 +45766,11 @@
       <c r="C36" s="199"/>
       <c r="D36" s="199"/>
       <c r="E36" s="200"/>
-      <c r="G36" s="307"/>
-      <c r="H36" s="308"/>
-      <c r="I36" s="308"/>
-      <c r="J36" s="308"/>
-      <c r="K36" s="309"/>
+      <c r="G36" s="308"/>
+      <c r="H36" s="309"/>
+      <c r="I36" s="309"/>
+      <c r="J36" s="309"/>
+      <c r="K36" s="310"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="198"/>
@@ -45834,11 +45778,11 @@
       <c r="C37" s="199"/>
       <c r="D37" s="199"/>
       <c r="E37" s="200"/>
-      <c r="G37" s="307"/>
-      <c r="H37" s="308"/>
-      <c r="I37" s="308"/>
-      <c r="J37" s="308"/>
-      <c r="K37" s="309"/>
+      <c r="G37" s="308"/>
+      <c r="H37" s="309"/>
+      <c r="I37" s="309"/>
+      <c r="J37" s="309"/>
+      <c r="K37" s="310"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="198"/>
@@ -45846,11 +45790,11 @@
       <c r="C38" s="199"/>
       <c r="D38" s="199"/>
       <c r="E38" s="200"/>
-      <c r="G38" s="307"/>
-      <c r="H38" s="308"/>
-      <c r="I38" s="308"/>
-      <c r="J38" s="308"/>
-      <c r="K38" s="309"/>
+      <c r="G38" s="308"/>
+      <c r="H38" s="309"/>
+      <c r="I38" s="309"/>
+      <c r="J38" s="309"/>
+      <c r="K38" s="310"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="198"/>
@@ -45858,11 +45802,11 @@
       <c r="C39" s="199"/>
       <c r="D39" s="199"/>
       <c r="E39" s="200"/>
-      <c r="G39" s="307"/>
-      <c r="H39" s="308"/>
-      <c r="I39" s="308"/>
-      <c r="J39" s="308"/>
-      <c r="K39" s="309"/>
+      <c r="G39" s="308"/>
+      <c r="H39" s="309"/>
+      <c r="I39" s="309"/>
+      <c r="J39" s="309"/>
+      <c r="K39" s="310"/>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="198"/>
@@ -45870,11 +45814,11 @@
       <c r="C40" s="199"/>
       <c r="D40" s="199"/>
       <c r="E40" s="200"/>
-      <c r="G40" s="307"/>
-      <c r="H40" s="308"/>
-      <c r="I40" s="308"/>
-      <c r="J40" s="308"/>
-      <c r="K40" s="309"/>
+      <c r="G40" s="308"/>
+      <c r="H40" s="309"/>
+      <c r="I40" s="309"/>
+      <c r="J40" s="309"/>
+      <c r="K40" s="310"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="201"/>
@@ -45882,11 +45826,11 @@
       <c r="C41" s="202"/>
       <c r="D41" s="202"/>
       <c r="E41" s="203"/>
-      <c r="G41" s="310"/>
-      <c r="H41" s="311"/>
-      <c r="I41" s="311"/>
-      <c r="J41" s="311"/>
-      <c r="K41" s="312"/>
+      <c r="G41" s="311"/>
+      <c r="H41" s="312"/>
+      <c r="I41" s="312"/>
+      <c r="J41" s="312"/>
+      <c r="K41" s="313"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="85"/>
@@ -45902,14 +45846,14 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="194" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="B43" s="194"/>
       <c r="C43" s="194"/>
       <c r="D43" s="194"/>
       <c r="E43" s="194"/>
       <c r="G43" s="194" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="H43" s="194"/>
       <c r="I43" s="194"/>
@@ -46092,12 +46036,6 @@
     <protectedRange sqref="D4" name="Range1_4_2_1_1_1"/>
   </protectedRanges>
   <mergeCells count="14">
-    <mergeCell ref="D2:K2"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="G9:K9"/>
-    <mergeCell ref="A10:E24"/>
-    <mergeCell ref="G10:K24"/>
     <mergeCell ref="A43:E43"/>
     <mergeCell ref="G43:K43"/>
     <mergeCell ref="A44:E57"/>
@@ -46106,6 +46044,12 @@
     <mergeCell ref="G26:K26"/>
     <mergeCell ref="A27:E41"/>
     <mergeCell ref="G27:K41"/>
+    <mergeCell ref="D2:K2"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="G9:K9"/>
+    <mergeCell ref="A10:E24"/>
+    <mergeCell ref="G10:K24"/>
   </mergeCells>
   <conditionalFormatting sqref="D7">
     <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
@@ -46156,16 +46100,16 @@
     <row r="2" spans="1:11" ht="23.25" x14ac:dyDescent="0.35">
       <c r="B2" s="81"/>
       <c r="C2" s="81"/>
-      <c r="D2" s="313" t="s">
+      <c r="D2" s="304" t="s">
         <v>197</v>
       </c>
-      <c r="E2" s="313"/>
-      <c r="F2" s="313"/>
-      <c r="G2" s="313"/>
-      <c r="H2" s="313"/>
-      <c r="I2" s="313"/>
-      <c r="J2" s="313"/>
-      <c r="K2" s="313"/>
+      <c r="E2" s="304"/>
+      <c r="F2" s="304"/>
+      <c r="G2" s="304"/>
+      <c r="H2" s="304"/>
+      <c r="I2" s="304"/>
+      <c r="J2" s="304"/>
+      <c r="K2" s="304"/>
     </row>
     <row r="3" spans="1:11" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A3" s="79"/>
@@ -46187,9 +46131,9 @@
       <c r="C4" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="D4" s="83" t="str">
+      <c r="D4" s="83">
         <f>SKOM!D4</f>
-        <v>24TS09B310</v>
+        <v>0</v>
       </c>
       <c r="E4" s="77"/>
       <c r="F4" s="77"/>
@@ -46205,9 +46149,9 @@
       <c r="C5" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="D5" s="77" t="str">
+      <c r="D5" s="77">
         <f>SKOM!D5</f>
-        <v>Gempol Ragas</v>
+        <v>0</v>
       </c>
       <c r="E5" s="78"/>
       <c r="F5" s="78"/>
@@ -46223,9 +46167,9 @@
       <c r="C6" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="D6" s="77" t="str">
+      <c r="D6" s="77">
         <f>SKOM!D6</f>
-        <v xml:space="preserve">TSEL </v>
+        <v>0</v>
       </c>
       <c r="E6" s="78"/>
       <c r="F6" s="78"/>
@@ -46253,14 +46197,14 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="194" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B9" s="194"/>
       <c r="C9" s="194"/>
       <c r="D9" s="194"/>
       <c r="E9" s="194"/>
       <c r="G9" s="194" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H9" s="194"/>
       <c r="I9" s="194"/>
@@ -46657,7 +46601,7 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="194" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B43" s="194"/>
       <c r="C43" s="194"/>
@@ -46829,14 +46773,14 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="194" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B58" s="194"/>
       <c r="C58" s="194"/>
       <c r="D58" s="194"/>
       <c r="E58" s="194"/>
       <c r="G58" s="194" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H58" s="194"/>
       <c r="I58" s="194"/>
@@ -47042,16 +46986,16 @@
     <row r="2" spans="1:11" ht="23.25" x14ac:dyDescent="0.35">
       <c r="B2" s="81"/>
       <c r="C2" s="81"/>
-      <c r="D2" s="313" t="s">
+      <c r="D2" s="304" t="s">
         <v>194</v>
       </c>
-      <c r="E2" s="313"/>
-      <c r="F2" s="313"/>
-      <c r="G2" s="313"/>
-      <c r="H2" s="313"/>
-      <c r="I2" s="313"/>
-      <c r="J2" s="313"/>
-      <c r="K2" s="313"/>
+      <c r="E2" s="304"/>
+      <c r="F2" s="304"/>
+      <c r="G2" s="304"/>
+      <c r="H2" s="304"/>
+      <c r="I2" s="304"/>
+      <c r="J2" s="304"/>
+      <c r="K2" s="304"/>
     </row>
     <row r="3" spans="1:11" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A3" s="79"/>
@@ -47073,9 +47017,9 @@
       <c r="C4" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="D4" s="83" t="str">
+      <c r="D4" s="83">
         <f>SKOM!D4</f>
-        <v>24TS09B310</v>
+        <v>0</v>
       </c>
       <c r="E4" s="77"/>
       <c r="F4" s="77"/>
@@ -47091,9 +47035,9 @@
       <c r="C5" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="D5" s="77" t="str">
+      <c r="D5" s="77">
         <f>SKOM!D5</f>
-        <v>Gempol Ragas</v>
+        <v>0</v>
       </c>
       <c r="E5" s="78"/>
       <c r="F5" s="78"/>
@@ -47109,9 +47053,9 @@
       <c r="C6" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="D6" s="77" t="str">
+      <c r="D6" s="77">
         <f>SKOM!D6</f>
-        <v xml:space="preserve">TSEL </v>
+        <v>0</v>
       </c>
       <c r="E6" s="78"/>
       <c r="F6" s="78"/>
@@ -47139,7 +47083,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="194" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B9" s="194"/>
       <c r="C9" s="194"/>
@@ -47342,7 +47286,7 @@
       <c r="D26" s="314"/>
       <c r="E26" s="314"/>
       <c r="G26" s="314" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H26" s="314"/>
       <c r="I26" s="314"/>
@@ -47519,14 +47463,14 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="314" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B42" s="314"/>
       <c r="C42" s="314"/>
       <c r="D42" s="314"/>
       <c r="E42" s="314"/>
       <c r="G42" s="314" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H42" s="314"/>
       <c r="I42" s="314"/>
@@ -47721,12 +47665,6 @@
     <protectedRange sqref="D4" name="Range1_4_2_1_1_1"/>
   </protectedRanges>
   <mergeCells count="14">
-    <mergeCell ref="D2:K2"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="G9:K9"/>
-    <mergeCell ref="A10:E24"/>
-    <mergeCell ref="G10:K24"/>
     <mergeCell ref="A43:E57"/>
     <mergeCell ref="G43:K57"/>
     <mergeCell ref="A26:E26"/>
@@ -47735,6 +47673,12 @@
     <mergeCell ref="G27:K40"/>
     <mergeCell ref="A42:E42"/>
     <mergeCell ref="G42:K42"/>
+    <mergeCell ref="D2:K2"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="G9:K9"/>
+    <mergeCell ref="A10:E24"/>
+    <mergeCell ref="G10:K24"/>
   </mergeCells>
   <conditionalFormatting sqref="D7">
     <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
@@ -47784,15 +47728,15 @@
     <row r="2" spans="1:11" ht="23.25" x14ac:dyDescent="0.35">
       <c r="B2" s="81"/>
       <c r="C2" s="81"/>
-      <c r="D2" s="313" t="s">
-        <v>210</v>
-      </c>
-      <c r="E2" s="313"/>
-      <c r="F2" s="313"/>
-      <c r="G2" s="313"/>
-      <c r="H2" s="313"/>
-      <c r="I2" s="313"/>
-      <c r="J2" s="313"/>
+      <c r="D2" s="304" t="s">
+        <v>209</v>
+      </c>
+      <c r="E2" s="304"/>
+      <c r="F2" s="304"/>
+      <c r="G2" s="304"/>
+      <c r="H2" s="304"/>
+      <c r="I2" s="304"/>
+      <c r="J2" s="304"/>
     </row>
     <row r="3" spans="1:11" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A3" s="79"/>
@@ -47814,9 +47758,9 @@
       <c r="C4" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="D4" s="83" t="str">
+      <c r="D4" s="83">
         <f>SKOM!D4</f>
-        <v>24TS09B310</v>
+        <v>0</v>
       </c>
       <c r="E4" s="77"/>
       <c r="F4" s="77"/>
@@ -47832,9 +47776,9 @@
       <c r="C5" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="D5" s="77" t="str">
+      <c r="D5" s="77">
         <f>SKOM!D5</f>
-        <v>Gempol Ragas</v>
+        <v>0</v>
       </c>
       <c r="E5" s="78"/>
       <c r="F5" s="78"/>
@@ -47850,9 +47794,9 @@
       <c r="C6" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="D6" s="77" t="str">
+      <c r="D6" s="77">
         <f>SKOM!D6</f>
-        <v xml:space="preserve">TSEL </v>
+        <v>0</v>
       </c>
       <c r="E6" s="78"/>
       <c r="F6" s="78"/>
@@ -47880,7 +47824,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="315" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B10" s="315"/>
       <c r="C10" s="315"/>
@@ -48484,14 +48428,14 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="315" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B63" s="315"/>
       <c r="C63" s="315"/>
       <c r="D63" s="315"/>
       <c r="E63" s="315"/>
       <c r="G63" s="315" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H63" s="315"/>
       <c r="I63" s="315"/>
@@ -48680,14 +48624,14 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="315" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B80" s="315"/>
       <c r="C80" s="315"/>
       <c r="D80" s="315"/>
       <c r="E80" s="315"/>
       <c r="G80" s="315" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H80" s="315"/>
       <c r="I80" s="315"/>
@@ -48876,14 +48820,14 @@
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="315" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B97" s="315"/>
       <c r="C97" s="315"/>
       <c r="D97" s="315"/>
       <c r="E97" s="315"/>
       <c r="G97" s="315" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H97" s="315"/>
       <c r="I97" s="315"/>
@@ -49085,7 +49029,7 @@
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" s="315" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B116" s="315"/>
       <c r="C116" s="315"/>
@@ -49893,14 +49837,14 @@
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A185" s="194" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B185" s="194"/>
       <c r="C185" s="194"/>
       <c r="D185" s="194"/>
       <c r="E185" s="194"/>
       <c r="G185" s="194" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="H185" s="194"/>
       <c r="I185" s="194"/>
@@ -50089,14 +50033,14 @@
     </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A202" s="194" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B202" s="194"/>
       <c r="C202" s="194"/>
       <c r="D202" s="194"/>
       <c r="E202" s="194"/>
       <c r="G202" s="194" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="H202" s="194"/>
       <c r="I202" s="194"/>
@@ -50291,27 +50235,20 @@
     <protectedRange sqref="D4" name="Range1_4_2_1_1_1_1"/>
   </protectedRanges>
   <mergeCells count="51">
-    <mergeCell ref="A203:E217"/>
-    <mergeCell ref="G203:K217"/>
-    <mergeCell ref="A185:E185"/>
-    <mergeCell ref="G185:K185"/>
-    <mergeCell ref="A186:E200"/>
-    <mergeCell ref="G186:K200"/>
-    <mergeCell ref="A202:E202"/>
-    <mergeCell ref="G202:K202"/>
-    <mergeCell ref="D2:J2"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="G10:K10"/>
-    <mergeCell ref="A11:E25"/>
-    <mergeCell ref="G11:K25"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="G27:K27"/>
-    <mergeCell ref="A28:E42"/>
-    <mergeCell ref="G28:K42"/>
-    <mergeCell ref="A114:K114"/>
-    <mergeCell ref="A98:E112"/>
-    <mergeCell ref="G64:K78"/>
+    <mergeCell ref="A168:E182"/>
+    <mergeCell ref="G168:K182"/>
+    <mergeCell ref="A150:E150"/>
+    <mergeCell ref="G150:K150"/>
+    <mergeCell ref="A151:E165"/>
+    <mergeCell ref="G151:K165"/>
+    <mergeCell ref="A167:E167"/>
+    <mergeCell ref="G167:K167"/>
+    <mergeCell ref="A117:E131"/>
+    <mergeCell ref="G117:K131"/>
+    <mergeCell ref="A133:E133"/>
+    <mergeCell ref="G133:K133"/>
+    <mergeCell ref="A134:E148"/>
+    <mergeCell ref="G134:K148"/>
     <mergeCell ref="A116:E116"/>
     <mergeCell ref="G116:K116"/>
     <mergeCell ref="A44:E44"/>
@@ -50328,20 +50265,27 @@
     <mergeCell ref="A81:E95"/>
     <mergeCell ref="A45:E59"/>
     <mergeCell ref="A64:E78"/>
-    <mergeCell ref="A117:E131"/>
-    <mergeCell ref="G117:K131"/>
-    <mergeCell ref="A133:E133"/>
-    <mergeCell ref="G133:K133"/>
-    <mergeCell ref="A134:E148"/>
-    <mergeCell ref="G134:K148"/>
-    <mergeCell ref="A168:E182"/>
-    <mergeCell ref="G168:K182"/>
-    <mergeCell ref="A150:E150"/>
-    <mergeCell ref="G150:K150"/>
-    <mergeCell ref="A151:E165"/>
-    <mergeCell ref="G151:K165"/>
-    <mergeCell ref="A167:E167"/>
-    <mergeCell ref="G167:K167"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="G27:K27"/>
+    <mergeCell ref="A28:E42"/>
+    <mergeCell ref="G28:K42"/>
+    <mergeCell ref="A114:K114"/>
+    <mergeCell ref="A98:E112"/>
+    <mergeCell ref="G64:K78"/>
+    <mergeCell ref="D2:J2"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="G10:K10"/>
+    <mergeCell ref="A11:E25"/>
+    <mergeCell ref="G11:K25"/>
+    <mergeCell ref="A203:E217"/>
+    <mergeCell ref="G203:K217"/>
+    <mergeCell ref="A185:E185"/>
+    <mergeCell ref="G185:K185"/>
+    <mergeCell ref="A186:E200"/>
+    <mergeCell ref="G186:K200"/>
+    <mergeCell ref="A202:E202"/>
+    <mergeCell ref="G202:K202"/>
   </mergeCells>
   <conditionalFormatting sqref="D7">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
@@ -51162,9 +51106,7 @@
       <c r="E5" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="F5" s="123" t="s">
-        <v>235</v>
-      </c>
+      <c r="F5" s="123"/>
       <c r="G5" s="121"/>
       <c r="H5" s="121"/>
     </row>
@@ -51176,9 +51118,7 @@
       <c r="E6" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="F6" s="125" t="s">
-        <v>230</v>
-      </c>
+      <c r="F6" s="125"/>
       <c r="G6" s="121"/>
     </row>
     <row r="7" spans="3:12" ht="15.75" x14ac:dyDescent="0.25">
@@ -51189,9 +51129,7 @@
       <c r="E7" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="F7" s="125" t="s">
-        <v>230</v>
-      </c>
+      <c r="F7" s="125"/>
       <c r="G7" s="121"/>
     </row>
     <row r="8" spans="3:12" ht="15.75" x14ac:dyDescent="0.25">
@@ -51202,9 +51140,7 @@
       <c r="E8" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="125" t="s">
-        <v>234</v>
-      </c>
+      <c r="F8" s="125"/>
       <c r="G8" s="121"/>
     </row>
     <row r="9" spans="3:12" ht="15.75" x14ac:dyDescent="0.25">
@@ -51215,33 +51151,25 @@
       <c r="E9" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="F9" s="185">
-        <v>45644</v>
-      </c>
+      <c r="F9" s="185"/>
       <c r="G9" s="121" t="s">
         <v>162</v>
       </c>
-      <c r="H9" s="185">
-        <v>45644</v>
-      </c>
+      <c r="H9" s="185"/>
     </row>
     <row r="10" spans="3:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C10" s="121" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D10" s="122"/>
       <c r="E10" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="F10" s="185">
-        <v>45839</v>
-      </c>
+      <c r="F10" s="185"/>
       <c r="G10" s="121" t="s">
         <v>162</v>
       </c>
-      <c r="H10" s="185">
-        <v>45839</v>
-      </c>
+      <c r="H10" s="185"/>
     </row>
     <row r="11" spans="3:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C11" s="121" t="s">
@@ -51251,9 +51179,7 @@
       <c r="E11" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="F11" s="126" t="s">
-        <v>203</v>
-      </c>
+      <c r="F11" s="126"/>
       <c r="G11" s="121"/>
     </row>
     <row r="12" spans="3:12" ht="15.75" x14ac:dyDescent="0.25">
@@ -51264,12 +51190,8 @@
       <c r="E12" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="F12" s="128" t="s">
-        <v>227</v>
-      </c>
-      <c r="G12" s="129" t="s">
-        <v>229</v>
-      </c>
+      <c r="F12" s="128"/>
+      <c r="G12" s="129"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
@@ -51282,9 +51204,7 @@
       <c r="E13" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="256" t="s">
-        <v>233</v>
-      </c>
+      <c r="F13" s="256"/>
       <c r="G13" s="257"/>
       <c r="H13" s="257"/>
       <c r="I13" s="257"/>
@@ -51301,9 +51221,7 @@
       <c r="F14" s="130" t="s">
         <v>167</v>
       </c>
-      <c r="G14" s="259" t="s">
-        <v>231</v>
-      </c>
+      <c r="G14" s="259"/>
       <c r="H14" s="260"/>
     </row>
     <row r="15" spans="3:12" ht="15.75" x14ac:dyDescent="0.25">
@@ -51313,9 +51231,7 @@
       <c r="F15" s="130" t="s">
         <v>168</v>
       </c>
-      <c r="G15" s="261" t="s">
-        <v>232</v>
-      </c>
+      <c r="G15" s="261"/>
       <c r="H15" s="262"/>
     </row>
     <row r="16" spans="3:12" ht="15.75" x14ac:dyDescent="0.25">
@@ -51326,9 +51242,7 @@
       <c r="E16" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="F16" s="125" t="s">
-        <v>218</v>
-      </c>
+      <c r="F16" s="125"/>
       <c r="G16" s="121"/>
     </row>
     <row r="17" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -51339,9 +51253,7 @@
       <c r="E17" s="121" t="s">
         <v>169</v>
       </c>
-      <c r="F17" s="131" t="s">
-        <v>221</v>
-      </c>
+      <c r="F17" s="131"/>
       <c r="G17" s="121"/>
     </row>
     <row r="18" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -51353,7 +51265,7 @@
         <v>169</v>
       </c>
       <c r="F18" s="131" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="G18" s="121"/>
     </row>
@@ -51431,9 +51343,7 @@
       <c r="E26" s="133" t="s">
         <v>169</v>
       </c>
-      <c r="F26" s="135" t="s">
-        <v>223</v>
-      </c>
+      <c r="F26" s="135"/>
     </row>
     <row r="27" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C27" s="254" t="s">
@@ -51443,9 +51353,7 @@
       <c r="E27" s="138" t="s">
         <v>65</v>
       </c>
-      <c r="F27" s="135" t="s">
-        <v>224</v>
-      </c>
+      <c r="F27" s="135"/>
     </row>
     <row r="28" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C28" s="254" t="s">
@@ -51455,9 +51363,7 @@
       <c r="E28" s="138" t="s">
         <v>65</v>
       </c>
-      <c r="F28" s="135" t="s">
-        <v>225</v>
-      </c>
+      <c r="F28" s="135"/>
     </row>
     <row r="29" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C29" s="254" t="s">
@@ -51527,16 +51433,16 @@
       <c r="I2" s="96"/>
     </row>
     <row r="3" spans="1:9" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A3" s="266" t="s">
+      <c r="A3" s="283" t="s">
         <v>180</v>
       </c>
-      <c r="B3" s="266"/>
-      <c r="C3" s="266"/>
-      <c r="D3" s="266"/>
-      <c r="E3" s="266"/>
-      <c r="F3" s="266"/>
-      <c r="G3" s="266"/>
-      <c r="H3" s="266"/>
+      <c r="B3" s="283"/>
+      <c r="C3" s="283"/>
+      <c r="D3" s="283"/>
+      <c r="E3" s="283"/>
+      <c r="F3" s="283"/>
+      <c r="G3" s="283"/>
+      <c r="H3" s="283"/>
       <c r="I3" s="97"/>
     </row>
     <row r="4" spans="1:9" ht="20.25" x14ac:dyDescent="0.25">
@@ -51547,9 +51453,9 @@
       <c r="C4" s="99" t="s">
         <v>65</v>
       </c>
-      <c r="D4" s="144" t="str">
-        <f>'MASTER '!F5</f>
-        <v>24TS09B310</v>
+      <c r="D4" s="144">
+        <f>MASTER!F5</f>
+        <v>0</v>
       </c>
       <c r="E4" s="143"/>
       <c r="F4" s="143"/>
@@ -51565,9 +51471,9 @@
       <c r="C5" s="99" t="s">
         <v>65</v>
       </c>
-      <c r="D5" s="145" t="str">
-        <f>'MASTER '!F7</f>
-        <v>Gempol Ragas</v>
+      <c r="D5" s="145">
+        <f>MASTER!F7</f>
+        <v>0</v>
       </c>
       <c r="E5" s="99"/>
       <c r="F5" s="100"/>
@@ -51583,9 +51489,9 @@
       <c r="C6" s="99" t="s">
         <v>65</v>
       </c>
-      <c r="D6" s="98" t="str">
-        <f>'MASTER '!F8</f>
-        <v>BKS395</v>
+      <c r="D6" s="98">
+        <f>MASTER!F8</f>
+        <v>0</v>
       </c>
       <c r="E6" s="99"/>
       <c r="F6" s="100"/>
@@ -51602,8 +51508,8 @@
         <v>65</v>
       </c>
       <c r="D7" s="146">
-        <f>'MASTER '!F10</f>
-        <v>45839</v>
+        <f>MASTER!F10</f>
+        <v>0</v>
       </c>
       <c r="E7" s="147"/>
       <c r="F7" s="100"/>
@@ -51623,39 +51529,39 @@
       <c r="I8" s="100"/>
     </row>
     <row r="9" spans="1:9" ht="18" x14ac:dyDescent="0.25">
-      <c r="A9" s="267" t="s">
+      <c r="A9" s="284" t="s">
         <v>66</v>
       </c>
-      <c r="B9" s="268"/>
+      <c r="B9" s="285"/>
       <c r="C9" s="148"/>
-      <c r="D9" s="271" t="s">
+      <c r="D9" s="288" t="s">
         <v>148</v>
       </c>
-      <c r="E9" s="273" t="s">
+      <c r="E9" s="290" t="s">
         <v>149</v>
       </c>
-      <c r="F9" s="275" t="s">
+      <c r="F9" s="292" t="s">
         <v>150</v>
       </c>
-      <c r="G9" s="275"/>
-      <c r="H9" s="276" t="s">
+      <c r="G9" s="292"/>
+      <c r="H9" s="293" t="s">
         <v>151</v>
       </c>
       <c r="I9" s="97"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="269"/>
-      <c r="B10" s="270"/>
+      <c r="A10" s="286"/>
+      <c r="B10" s="287"/>
       <c r="C10" s="102"/>
-      <c r="D10" s="272"/>
-      <c r="E10" s="274"/>
+      <c r="D10" s="289"/>
+      <c r="E10" s="291"/>
       <c r="F10" s="103" t="s">
         <v>152</v>
       </c>
       <c r="G10" s="103" t="s">
         <v>153</v>
       </c>
-      <c r="H10" s="277"/>
+      <c r="H10" s="294"/>
       <c r="I10" s="97"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -51675,10 +51581,10 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="149"/>
-      <c r="B12" s="278">
+      <c r="B12" s="277">
         <v>1</v>
       </c>
-      <c r="C12" s="280"/>
+      <c r="C12" s="279"/>
       <c r="D12" s="111" t="s">
         <v>182</v>
       </c>
@@ -51692,10 +51598,10 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="149"/>
-      <c r="B13" s="278">
+      <c r="B13" s="277">
         <v>2</v>
       </c>
-      <c r="C13" s="281"/>
+      <c r="C13" s="282"/>
       <c r="D13" s="111" t="s">
         <v>183</v>
       </c>
@@ -51709,10 +51615,10 @@
     </row>
     <row r="14" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="149"/>
-      <c r="B14" s="278">
+      <c r="B14" s="277">
         <v>3</v>
       </c>
-      <c r="C14" s="280"/>
+      <c r="C14" s="279"/>
       <c r="D14" s="114" t="s">
         <v>184</v>
       </c>
@@ -51726,11 +51632,11 @@
     </row>
     <row r="15" spans="1:9" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="149"/>
-      <c r="B15" s="278">
+      <c r="B15" s="277">
         <f t="shared" ref="B15:B17" si="0">B14+1</f>
         <v>4</v>
       </c>
-      <c r="C15" s="280"/>
+      <c r="C15" s="279"/>
       <c r="D15" s="114" t="s">
         <v>185</v>
       </c>
@@ -51744,10 +51650,10 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="149"/>
-      <c r="B16" s="278">
+      <c r="B16" s="277">
         <v>5</v>
       </c>
-      <c r="C16" s="280"/>
+      <c r="C16" s="279"/>
       <c r="D16" s="111" t="s">
         <v>186</v>
       </c>
@@ -51761,11 +51667,11 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="149"/>
-      <c r="B17" s="278">
+      <c r="B17" s="277">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C17" s="280"/>
+      <c r="C17" s="279"/>
       <c r="D17" s="111" t="s">
         <v>187</v>
       </c>
@@ -51779,10 +51685,10 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="152"/>
-      <c r="B18" s="278">
+      <c r="B18" s="277">
         <v>7</v>
       </c>
-      <c r="C18" s="280"/>
+      <c r="C18" s="279"/>
       <c r="D18" s="115" t="s">
         <v>188</v>
       </c>
@@ -51798,10 +51704,10 @@
       <c r="A19" s="149">
         <v>2</v>
       </c>
-      <c r="B19" s="278">
+      <c r="B19" s="277">
         <v>8</v>
       </c>
-      <c r="C19" s="280"/>
+      <c r="C19" s="279"/>
       <c r="D19" s="111" t="s">
         <v>189</v>
       </c>
@@ -51815,8 +51721,8 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="152"/>
-      <c r="B20" s="278"/>
-      <c r="C20" s="280"/>
+      <c r="B20" s="277"/>
+      <c r="C20" s="279"/>
       <c r="D20" s="111"/>
       <c r="E20" s="112"/>
       <c r="F20" s="113"/>
@@ -51826,8 +51732,8 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="152"/>
-      <c r="B21" s="278"/>
-      <c r="C21" s="280"/>
+      <c r="B21" s="277"/>
+      <c r="C21" s="279"/>
       <c r="D21" s="111"/>
       <c r="E21" s="112"/>
       <c r="F21" s="113"/>
@@ -51837,8 +51743,8 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="152"/>
-      <c r="B22" s="278"/>
-      <c r="C22" s="280"/>
+      <c r="B22" s="277"/>
+      <c r="C22" s="279"/>
       <c r="D22" s="111"/>
       <c r="E22" s="112"/>
       <c r="F22" s="108"/>
@@ -51859,8 +51765,8 @@
     </row>
     <row r="24" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="152"/>
-      <c r="B24" s="278"/>
-      <c r="C24" s="279"/>
+      <c r="B24" s="277"/>
+      <c r="C24" s="278"/>
       <c r="D24" s="111"/>
       <c r="E24" s="112"/>
       <c r="F24" s="108"/>
@@ -51870,8 +51776,8 @@
     </row>
     <row r="25" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="152"/>
-      <c r="B25" s="278"/>
-      <c r="C25" s="279"/>
+      <c r="B25" s="277"/>
+      <c r="C25" s="278"/>
       <c r="D25" s="111"/>
       <c r="E25" s="112"/>
       <c r="F25" s="108"/>
@@ -51903,8 +51809,8 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="156"/>
-      <c r="B28" s="278"/>
-      <c r="C28" s="280"/>
+      <c r="B28" s="277"/>
+      <c r="C28" s="279"/>
       <c r="D28" s="111"/>
       <c r="E28" s="112"/>
       <c r="F28" s="108"/>
@@ -51914,8 +51820,8 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="156"/>
-      <c r="B29" s="278"/>
-      <c r="C29" s="280"/>
+      <c r="B29" s="277"/>
+      <c r="C29" s="279"/>
       <c r="D29" s="111"/>
       <c r="E29" s="112"/>
       <c r="F29" s="108"/>
@@ -51925,8 +51831,8 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="156"/>
-      <c r="B30" s="278"/>
-      <c r="C30" s="280"/>
+      <c r="B30" s="277"/>
+      <c r="C30" s="279"/>
       <c r="D30" s="111"/>
       <c r="E30" s="112"/>
       <c r="F30" s="108"/>
@@ -51958,8 +51864,8 @@
     </row>
     <row r="33" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="160"/>
-      <c r="B33" s="293"/>
-      <c r="C33" s="294"/>
+      <c r="B33" s="280"/>
+      <c r="C33" s="281"/>
       <c r="D33" s="161"/>
       <c r="E33" s="162"/>
       <c r="F33" s="163"/>
@@ -52016,19 +51922,19 @@
       <c r="I37" s="96"/>
     </row>
     <row r="38" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="287" t="str">
-        <f>'MASTER '!F18</f>
+      <c r="A38" s="271" t="str">
+        <f>MASTER!F18</f>
         <v>PT. TRITECH CONSULT INDONESIA</v>
       </c>
-      <c r="B38" s="288"/>
-      <c r="C38" s="288"/>
-      <c r="D38" s="289"/>
+      <c r="B38" s="272"/>
+      <c r="C38" s="272"/>
+      <c r="D38" s="273"/>
       <c r="E38" s="172"/>
-      <c r="F38" s="282" t="s">
+      <c r="F38" s="266" t="s">
         <v>191</v>
       </c>
-      <c r="G38" s="283"/>
-      <c r="H38" s="284"/>
+      <c r="G38" s="267"/>
+      <c r="H38" s="268"/>
       <c r="I38" s="96"/>
     </row>
     <row r="39" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -52036,8 +51942,8 @@
         <v>156</v>
       </c>
       <c r="B39" s="174"/>
-      <c r="C39" s="285"/>
-      <c r="D39" s="286"/>
+      <c r="C39" s="269"/>
+      <c r="D39" s="270"/>
       <c r="E39" s="168"/>
       <c r="F39" s="173" t="s">
         <v>156</v>
@@ -52074,9 +51980,9 @@
       <c r="C42" s="172"/>
       <c r="D42" s="180"/>
       <c r="E42" s="172"/>
-      <c r="F42" s="287"/>
-      <c r="G42" s="288"/>
-      <c r="H42" s="289"/>
+      <c r="F42" s="271"/>
+      <c r="G42" s="272"/>
+      <c r="H42" s="273"/>
       <c r="I42" s="96"/>
     </row>
     <row r="43" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -52085,23 +51991,19 @@
       <c r="C43" s="182"/>
       <c r="D43" s="183"/>
       <c r="E43" s="168"/>
-      <c r="F43" s="290"/>
-      <c r="G43" s="291"/>
-      <c r="H43" s="292"/>
+      <c r="F43" s="274"/>
+      <c r="G43" s="275"/>
+      <c r="H43" s="276"/>
       <c r="I43" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A9:B10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H9:H10"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
@@ -52114,12 +52016,16 @@
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="B22:C22"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A9:B10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A38:D38"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="75" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
@@ -52150,7 +52056,7 @@
       <c r="B2" s="81"/>
       <c r="C2" s="81"/>
       <c r="D2" s="193" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E2" s="193"/>
       <c r="F2" s="193"/>
@@ -52180,9 +52086,9 @@
       <c r="C4" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="D4" s="83" t="str">
-        <f>'MASTER '!F5</f>
-        <v>24TS09B310</v>
+      <c r="D4" s="83">
+        <f>MASTER!F5</f>
+        <v>0</v>
       </c>
       <c r="E4" s="77"/>
       <c r="F4" s="77"/>
@@ -52198,9 +52104,9 @@
       <c r="C5" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="D5" s="77" t="str">
-        <f>'MASTER '!F7</f>
-        <v>Gempol Ragas</v>
+      <c r="D5" s="77">
+        <f>MASTER!F7</f>
+        <v>0</v>
       </c>
       <c r="E5" s="78"/>
       <c r="F5" s="78"/>
@@ -52246,7 +52152,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="194" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B9" s="194"/>
       <c r="C9" s="194"/>
@@ -52585,7 +52491,7 @@
       <c r="B2" s="81"/>
       <c r="C2" s="81"/>
       <c r="D2" s="193" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E2" s="193"/>
       <c r="F2" s="193"/>
@@ -52615,9 +52521,9 @@
       <c r="C4" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="D4" s="83" t="str">
-        <f>'MASTER '!F5</f>
-        <v>24TS09B310</v>
+      <c r="D4" s="83">
+        <f>MASTER!F5</f>
+        <v>0</v>
       </c>
       <c r="E4" s="77"/>
       <c r="F4" s="77"/>
@@ -52633,9 +52539,9 @@
       <c r="C5" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="D5" s="77" t="str">
-        <f>'MASTER '!F7</f>
-        <v>Gempol Ragas</v>
+      <c r="D5" s="77">
+        <f>MASTER!F7</f>
+        <v>0</v>
       </c>
       <c r="E5" s="78"/>
       <c r="F5" s="78"/>
@@ -52681,7 +52587,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="194" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B9" s="194"/>
       <c r="C9" s="194"/>
@@ -53227,7 +53133,7 @@
       <c r="B2" s="81"/>
       <c r="C2" s="81"/>
       <c r="D2" s="193" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E2" s="193"/>
       <c r="F2" s="193"/>
@@ -53257,9 +53163,9 @@
       <c r="C4" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="D4" s="83" t="str">
-        <f>'MASTER '!F5</f>
-        <v>24TS09B310</v>
+      <c r="D4" s="83">
+        <f>MASTER!F5</f>
+        <v>0</v>
       </c>
       <c r="E4" s="77"/>
       <c r="F4" s="77"/>
@@ -53275,9 +53181,9 @@
       <c r="C5" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="D5" s="77" t="str">
-        <f>'MASTER '!F7</f>
-        <v>Gempol Ragas</v>
+      <c r="D5" s="77">
+        <f>MASTER!F7</f>
+        <v>0</v>
       </c>
       <c r="E5" s="78"/>
       <c r="F5" s="78"/>
@@ -53323,7 +53229,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="194" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B9" s="194"/>
       <c r="C9" s="194"/>
@@ -53674,7 +53580,7 @@
       <c r="B2" s="81"/>
       <c r="C2" s="81"/>
       <c r="D2" s="193" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E2" s="193"/>
       <c r="F2" s="193"/>
@@ -53704,9 +53610,9 @@
       <c r="C4" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="D4" s="83" t="str">
-        <f>'MASTER '!F5</f>
-        <v>24TS09B310</v>
+      <c r="D4" s="83">
+        <f>MASTER!F5</f>
+        <v>0</v>
       </c>
       <c r="E4" s="77"/>
       <c r="F4" s="77"/>
@@ -53722,9 +53628,9 @@
       <c r="C5" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="D5" s="77" t="str">
-        <f>'MASTER '!F7</f>
-        <v>Gempol Ragas</v>
+      <c r="D5" s="77">
+        <f>MASTER!F7</f>
+        <v>0</v>
       </c>
       <c r="E5" s="78"/>
       <c r="F5" s="78"/>
@@ -53770,7 +53676,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="194" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B9" s="194"/>
       <c r="C9" s="194"/>
@@ -54355,7 +54261,7 @@
       <c r="B2" s="81"/>
       <c r="C2" s="81"/>
       <c r="D2" s="193" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E2" s="193"/>
       <c r="F2" s="193"/>
@@ -54385,9 +54291,9 @@
       <c r="C4" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="D4" s="83" t="str">
-        <f>'MASTER '!F5</f>
-        <v>24TS09B310</v>
+      <c r="D4" s="83">
+        <f>MASTER!F5</f>
+        <v>0</v>
       </c>
       <c r="E4" s="77"/>
       <c r="F4" s="77"/>
@@ -54403,9 +54309,9 @@
       <c r="C5" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="D5" s="77" t="str">
-        <f>'MASTER '!F7</f>
-        <v>Gempol Ragas</v>
+      <c r="D5" s="77">
+        <f>MASTER!F7</f>
+        <v>0</v>
       </c>
       <c r="E5" s="78"/>
       <c r="F5" s="78"/>
@@ -54451,7 +54357,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="194" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B9" s="194"/>
       <c r="C9" s="194"/>
